--- a/research/traditional_assets/database/data/belgium/belgium_environmental_waste_services.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_environmental_waste_services.xlsx
@@ -1403,7 +1403,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1540,22 +1540,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08706091900117428</v>
+        <v>0.08687701670367134</v>
       </c>
       <c r="C2">
-        <v>78.34890104808515</v>
+        <v>77.78403340605597</v>
       </c>
       <c r="D2">
-        <v>69.71890104808516</v>
+        <v>70.03103340605597</v>
       </c>
       <c r="E2">
-        <v>-33.4</v>
+        <v>-32.523</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.8769999999999999</v>
       </c>
       <c r="G2">
         <v>8.630000000000001</v>
@@ -1576,28 +1576,28 @@
         <v>4.57</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0441131</v>
       </c>
       <c r="N2">
-        <v>4.57</v>
+        <v>4.525886900000001</v>
       </c>
       <c r="O2">
-        <v>1.1425</v>
+        <v>1.131471725</v>
       </c>
       <c r="P2">
-        <v>3.4275</v>
+        <v>3.394415175000001</v>
       </c>
       <c r="Q2">
-        <v>11.0075</v>
+        <v>10.974415175</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08706091900117428</v>
+        <v>0.08737350172088015</v>
       </c>
       <c r="T2">
-        <v>0.8042521102410373</v>
+        <v>0.8103449292580148</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>103.5973440995986</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1622,22 +1622,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08687701670367134</v>
+        <v>0.08669311440616842</v>
       </c>
       <c r="C3">
-        <v>77.78403340605597</v>
+        <v>77.2219731734691</v>
       </c>
       <c r="D3">
-        <v>70.03103340605597</v>
+        <v>70.3459731734691</v>
       </c>
       <c r="E3">
-        <v>-32.523</v>
+        <v>-31.646</v>
       </c>
       <c r="F3">
-        <v>0.8769999999999999</v>
+        <v>1.754</v>
       </c>
       <c r="G3">
         <v>8.630000000000001</v>
@@ -1658,28 +1658,28 @@
         <v>4.57</v>
       </c>
       <c r="M3">
-        <v>0.0441131</v>
+        <v>0.08822619999999999</v>
       </c>
       <c r="N3">
-        <v>4.525886900000001</v>
+        <v>4.4817738</v>
       </c>
       <c r="O3">
-        <v>1.131471725</v>
+        <v>1.12044345</v>
       </c>
       <c r="P3">
-        <v>3.394415175000001</v>
+        <v>3.36133035</v>
       </c>
       <c r="Q3">
-        <v>10.974415175</v>
+        <v>10.94133035</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08737350172088015</v>
+        <v>0.08769246367976369</v>
       </c>
       <c r="T3">
-        <v>0.8103449292580148</v>
+        <v>0.8165620915202368</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>103.5973440995986</v>
+        <v>51.79867204979927</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1704,22 +1704,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08669311440616842</v>
+        <v>0.08650921210866547</v>
       </c>
       <c r="C4">
-        <v>77.2219731734691</v>
+        <v>76.6627583974167</v>
       </c>
       <c r="D4">
-        <v>70.3459731734691</v>
+        <v>70.6637583974167</v>
       </c>
       <c r="E4">
-        <v>-31.646</v>
+        <v>-30.769</v>
       </c>
       <c r="F4">
-        <v>1.754</v>
+        <v>2.631</v>
       </c>
       <c r="G4">
         <v>8.630000000000001</v>
@@ -1740,28 +1740,28 @@
         <v>4.57</v>
       </c>
       <c r="M4">
-        <v>0.08822619999999999</v>
+        <v>0.1323393</v>
       </c>
       <c r="N4">
-        <v>4.4817738</v>
+        <v>4.4376607</v>
       </c>
       <c r="O4">
-        <v>1.12044345</v>
+        <v>1.109415175</v>
       </c>
       <c r="P4">
-        <v>3.36133035</v>
+        <v>3.328245525</v>
       </c>
       <c r="Q4">
-        <v>10.94133035</v>
+        <v>10.908245525</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08769246367976369</v>
+        <v>0.08801800217388192</v>
       </c>
       <c r="T4">
-        <v>0.8165620915202368</v>
+        <v>0.8229074426950819</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>51.79867204979927</v>
+        <v>34.53244803319951</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1786,22 +1786,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08650921210866547</v>
+        <v>0.08632530981116254</v>
       </c>
       <c r="C5">
-        <v>76.6627583974167</v>
+        <v>76.10642781561562</v>
       </c>
       <c r="D5">
-        <v>70.6637583974167</v>
+        <v>70.98442781561562</v>
       </c>
       <c r="E5">
-        <v>-30.769</v>
+        <v>-29.892</v>
       </c>
       <c r="F5">
-        <v>2.631</v>
+        <v>3.508</v>
       </c>
       <c r="G5">
         <v>8.630000000000001</v>
@@ -1822,28 +1822,28 @@
         <v>4.57</v>
       </c>
       <c r="M5">
-        <v>0.1323393</v>
+        <v>0.1764524</v>
       </c>
       <c r="N5">
-        <v>4.4376607</v>
+        <v>4.393547600000001</v>
       </c>
       <c r="O5">
-        <v>1.109415175</v>
+        <v>1.0983869</v>
       </c>
       <c r="P5">
-        <v>3.328245525</v>
+        <v>3.2951607</v>
       </c>
       <c r="Q5">
-        <v>10.908245525</v>
+        <v>10.8751607</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08801800217388192</v>
+        <v>0.08835032271996099</v>
       </c>
       <c r="T5">
-        <v>0.8229074426950819</v>
+        <v>0.8293849886860697</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>34.53244803319951</v>
+        <v>25.89933602489964</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1868,22 +1868,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08632530981116254</v>
+        <v>0.0861414075136596</v>
       </c>
       <c r="C6">
-        <v>76.10642781561562</v>
+        <v>75.55302087214947</v>
       </c>
       <c r="D6">
-        <v>70.98442781561562</v>
+        <v>71.30802087214948</v>
       </c>
       <c r="E6">
-        <v>-29.892</v>
+        <v>-29.015</v>
       </c>
       <c r="F6">
-        <v>3.508</v>
+        <v>4.385</v>
       </c>
       <c r="G6">
         <v>8.630000000000001</v>
@@ -1904,28 +1904,28 @@
         <v>4.57</v>
       </c>
       <c r="M6">
-        <v>0.1764524</v>
+        <v>0.2205655</v>
       </c>
       <c r="N6">
-        <v>4.393547600000001</v>
+        <v>4.3494345</v>
       </c>
       <c r="O6">
-        <v>1.0983869</v>
+        <v>1.087358625</v>
       </c>
       <c r="P6">
-        <v>3.2951607</v>
+        <v>3.262075875</v>
       </c>
       <c r="Q6">
-        <v>10.8751607</v>
+        <v>10.842075875</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08835032271996099</v>
+        <v>0.08868963948806274</v>
       </c>
       <c r="T6">
-        <v>0.8293849886860697</v>
+        <v>0.8359989040663414</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>25.89933602489964</v>
+        <v>20.71946881991971</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1950,22 +1950,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0861414075136596</v>
+        <v>0.08595750521615667</v>
       </c>
       <c r="C7">
-        <v>75.55302087214947</v>
+        <v>75.00257773364245</v>
       </c>
       <c r="D7">
-        <v>71.30802087214948</v>
+        <v>71.63457773364246</v>
       </c>
       <c r="E7">
-        <v>-29.015</v>
+        <v>-28.138</v>
       </c>
       <c r="F7">
-        <v>4.385</v>
+        <v>5.262</v>
       </c>
       <c r="G7">
         <v>8.630000000000001</v>
@@ -1986,28 +1986,28 @@
         <v>4.57</v>
       </c>
       <c r="M7">
-        <v>0.2205655</v>
+        <v>0.2646786</v>
       </c>
       <c r="N7">
-        <v>4.3494345</v>
+        <v>4.3053214</v>
       </c>
       <c r="O7">
-        <v>1.087358625</v>
+        <v>1.07633035</v>
       </c>
       <c r="P7">
-        <v>3.262075875</v>
+        <v>3.22899105</v>
       </c>
       <c r="Q7">
-        <v>10.842075875</v>
+        <v>10.80899105</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08868963948806274</v>
+        <v>0.0890361757618688</v>
       </c>
       <c r="T7">
-        <v>0.8359989040663414</v>
+        <v>0.8427535410504486</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2024,7 +2024,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>20.71946881991971</v>
+        <v>17.26622401659976</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2032,22 +2032,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08595750521615667</v>
+        <v>0.08577360291865373</v>
       </c>
       <c r="C8">
-        <v>75.00257773364245</v>
+        <v>74.45513930587997</v>
       </c>
       <c r="D8">
-        <v>71.63457773364246</v>
+        <v>71.96413930587997</v>
       </c>
       <c r="E8">
-        <v>-28.138</v>
+        <v>-27.261</v>
       </c>
       <c r="F8">
-        <v>5.262</v>
+        <v>6.138999999999998</v>
       </c>
       <c r="G8">
         <v>8.630000000000001</v>
@@ -2068,28 +2068,28 @@
         <v>4.57</v>
       </c>
       <c r="M8">
-        <v>0.2646786</v>
+        <v>0.3087916999999999</v>
       </c>
       <c r="N8">
-        <v>4.3053214</v>
+        <v>4.261208300000001</v>
       </c>
       <c r="O8">
-        <v>1.07633035</v>
+        <v>1.065302075</v>
       </c>
       <c r="P8">
-        <v>3.22899105</v>
+        <v>3.195906225000001</v>
       </c>
       <c r="Q8">
-        <v>10.80899105</v>
+        <v>10.775906225</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.0890361757618688</v>
+        <v>0.08939016442865992</v>
       </c>
       <c r="T8">
-        <v>0.8427535410504486</v>
+        <v>0.8496534390449667</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>17.26622401659976</v>
+        <v>14.79962058565694</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2114,22 +2114,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08577360291865371</v>
+        <v>0.08558970062115082</v>
       </c>
       <c r="C9">
-        <v>74.45513930588</v>
+        <v>73.91074725089013</v>
       </c>
       <c r="D9">
-        <v>71.96413930588</v>
+        <v>72.29674725089014</v>
       </c>
       <c r="E9">
-        <v>-27.261</v>
+        <v>-26.384</v>
       </c>
       <c r="F9">
-        <v>6.138999999999999</v>
+        <v>7.015999999999999</v>
       </c>
       <c r="G9">
         <v>8.630000000000001</v>
@@ -2150,28 +2150,28 @@
         <v>4.57</v>
       </c>
       <c r="M9">
-        <v>0.3087916999999999</v>
+        <v>0.3529048</v>
       </c>
       <c r="N9">
-        <v>4.261208300000001</v>
+        <v>4.2170952</v>
       </c>
       <c r="O9">
-        <v>1.065302075</v>
+        <v>1.0542738</v>
       </c>
       <c r="P9">
-        <v>3.195906225000001</v>
+        <v>3.1628214</v>
       </c>
       <c r="Q9">
-        <v>10.775906225</v>
+        <v>10.7428214</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08939016442865992</v>
+        <v>0.08975184850125087</v>
       </c>
       <c r="T9">
-        <v>0.8496534390449667</v>
+        <v>0.8567033348219746</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>14.79962058565694</v>
+        <v>12.94966801244982</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2196,22 +2196,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08558970062115082</v>
+        <v>0.08550704832364786</v>
       </c>
       <c r="C10">
-        <v>73.91074725089013</v>
+        <v>73.1842367109369</v>
       </c>
       <c r="D10">
-        <v>72.29674725089014</v>
+        <v>72.44723671093691</v>
       </c>
       <c r="E10">
-        <v>-26.384</v>
+        <v>-25.507</v>
       </c>
       <c r="F10">
-        <v>7.015999999999999</v>
+        <v>7.892999999999999</v>
       </c>
       <c r="G10">
         <v>8.630000000000001</v>
@@ -2232,45 +2232,45 @@
         <v>4.57</v>
       </c>
       <c r="M10">
-        <v>0.3529048</v>
+        <v>0.4088573999999999</v>
       </c>
       <c r="N10">
-        <v>4.2170952</v>
+        <v>4.161142600000001</v>
       </c>
       <c r="O10">
-        <v>1.0542738</v>
+        <v>1.04028565</v>
       </c>
       <c r="P10">
-        <v>3.1628214</v>
+        <v>3.12085695</v>
       </c>
       <c r="Q10">
-        <v>10.7428214</v>
+        <v>10.70085695</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08975184850125087</v>
+        <v>0.09012148167433831</v>
       </c>
       <c r="T10">
-        <v>0.8567033348219746</v>
+        <v>0.8639081733633119</v>
       </c>
       <c r="U10">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.25</v>
       </c>
       <c r="W10">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>12.94966801244982</v>
+        <v>11.17749122310126</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2278,22 +2278,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08550704832364786</v>
+        <v>0.08533439602614493</v>
       </c>
       <c r="C11">
-        <v>73.1842367109369</v>
+        <v>72.62362403749705</v>
       </c>
       <c r="D11">
-        <v>72.44723671093691</v>
+        <v>72.76362403749705</v>
       </c>
       <c r="E11">
-        <v>-25.507</v>
+        <v>-24.63</v>
       </c>
       <c r="F11">
-        <v>7.892999999999999</v>
+        <v>8.769999999999998</v>
       </c>
       <c r="G11">
         <v>8.630000000000001</v>
@@ -2314,28 +2314,28 @@
         <v>4.57</v>
       </c>
       <c r="M11">
-        <v>0.4088573999999999</v>
+        <v>0.4542859999999999</v>
       </c>
       <c r="N11">
-        <v>4.161142600000001</v>
+        <v>4.115714000000001</v>
       </c>
       <c r="O11">
-        <v>1.04028565</v>
+        <v>1.0289285</v>
       </c>
       <c r="P11">
-        <v>3.12085695</v>
+        <v>3.0867855</v>
       </c>
       <c r="Q11">
-        <v>10.70085695</v>
+        <v>10.6667855</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09012148167433831</v>
+        <v>0.0904993289179388</v>
       </c>
       <c r="T11">
-        <v>0.8639081733633119</v>
+        <v>0.8712731194277903</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.17749122310126</v>
+        <v>10.05974210079114</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2360,22 +2360,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08533439602614493</v>
+        <v>0.08530199372864199</v>
       </c>
       <c r="C12">
-        <v>72.62362403749705</v>
+        <v>71.80630985005757</v>
       </c>
       <c r="D12">
-        <v>72.76362403749705</v>
+        <v>72.82330985005758</v>
       </c>
       <c r="E12">
-        <v>-24.63</v>
+        <v>-23.753</v>
       </c>
       <c r="F12">
-        <v>8.77</v>
+        <v>9.646999999999998</v>
       </c>
       <c r="G12">
         <v>8.630000000000001</v>
@@ -2396,45 +2396,45 @@
         <v>4.57</v>
       </c>
       <c r="M12">
-        <v>0.454286</v>
+        <v>0.5161144999999999</v>
       </c>
       <c r="N12">
-        <v>4.115714000000001</v>
+        <v>4.053885500000001</v>
       </c>
       <c r="O12">
-        <v>1.0289285</v>
+        <v>1.013471375</v>
       </c>
       <c r="P12">
-        <v>3.0867855</v>
+        <v>3.040414125000001</v>
       </c>
       <c r="Q12">
-        <v>10.6667855</v>
+        <v>10.620414125</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0904993289179388</v>
+        <v>0.09088566711083369</v>
       </c>
       <c r="T12">
-        <v>0.8712731194277903</v>
+        <v>0.8788035698982121</v>
       </c>
       <c r="U12">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>10.05974210079113</v>
+        <v>8.854624313015815</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2442,22 +2442,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08530199372864199</v>
+        <v>0.08514209143113904</v>
       </c>
       <c r="C13">
-        <v>71.80630985005757</v>
+        <v>71.22529346793856</v>
       </c>
       <c r="D13">
-        <v>72.82330985005758</v>
+        <v>73.11929346793856</v>
       </c>
       <c r="E13">
-        <v>-23.753</v>
+        <v>-22.876</v>
       </c>
       <c r="F13">
-        <v>9.646999999999998</v>
+        <v>10.524</v>
       </c>
       <c r="G13">
         <v>8.630000000000001</v>
@@ -2478,28 +2478,28 @@
         <v>4.57</v>
       </c>
       <c r="M13">
-        <v>0.5161144999999999</v>
+        <v>0.5630339999999999</v>
       </c>
       <c r="N13">
-        <v>4.053885500000001</v>
+        <v>4.006966</v>
       </c>
       <c r="O13">
-        <v>1.013471375</v>
+        <v>1.0017415</v>
       </c>
       <c r="P13">
-        <v>3.040414125000001</v>
+        <v>3.0052245</v>
       </c>
       <c r="Q13">
-        <v>10.620414125</v>
+        <v>10.5852245</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09088566711083369</v>
+        <v>0.09128078571720347</v>
       </c>
       <c r="T13">
-        <v>0.8788035698982121</v>
+        <v>0.8865051669702343</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>8.854624313015815</v>
+        <v>8.116738953597832</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2524,22 +2524,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08514209143113904</v>
+        <v>0.08506018913363611</v>
       </c>
       <c r="C14">
-        <v>71.22529346793856</v>
+        <v>70.50083063749805</v>
       </c>
       <c r="D14">
-        <v>73.11929346793856</v>
+        <v>73.27183063749806</v>
       </c>
       <c r="E14">
-        <v>-22.876</v>
+        <v>-21.999</v>
       </c>
       <c r="F14">
-        <v>10.524</v>
+        <v>11.401</v>
       </c>
       <c r="G14">
         <v>8.630000000000001</v>
@@ -2560,45 +2560,45 @@
         <v>4.57</v>
       </c>
       <c r="M14">
-        <v>0.5630339999999999</v>
+        <v>0.6190742999999999</v>
       </c>
       <c r="N14">
-        <v>4.006966</v>
+        <v>3.9509257</v>
       </c>
       <c r="O14">
-        <v>1.0017415</v>
+        <v>0.9877314250000001</v>
       </c>
       <c r="P14">
-        <v>3.0052245</v>
+        <v>2.963194275</v>
       </c>
       <c r="Q14">
-        <v>10.5852245</v>
+        <v>10.543194275</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09128078571720347</v>
+        <v>0.09168498750992657</v>
       </c>
       <c r="T14">
-        <v>0.8865051669702343</v>
+        <v>0.8943838122508087</v>
       </c>
       <c r="U14">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y14">
-        <v>8.116738953597832</v>
+        <v>7.381989528559013</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2606,22 +2606,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08506018913363611</v>
+        <v>0.08490628683613317</v>
       </c>
       <c r="C15">
-        <v>70.50083063749805</v>
+        <v>69.9121910007463</v>
       </c>
       <c r="D15">
-        <v>73.27183063749806</v>
+        <v>73.5601910007463</v>
       </c>
       <c r="E15">
-        <v>-21.999</v>
+        <v>-21.122</v>
       </c>
       <c r="F15">
-        <v>11.401</v>
+        <v>12.278</v>
       </c>
       <c r="G15">
         <v>8.630000000000001</v>
@@ -2642,28 +2642,28 @@
         <v>4.57</v>
       </c>
       <c r="M15">
-        <v>0.6190742999999999</v>
+        <v>0.6666953999999999</v>
       </c>
       <c r="N15">
-        <v>3.9509257</v>
+        <v>3.9033046</v>
       </c>
       <c r="O15">
-        <v>0.9877314250000001</v>
+        <v>0.9758261500000001</v>
       </c>
       <c r="P15">
-        <v>2.963194275</v>
+        <v>2.92747845</v>
       </c>
       <c r="Q15">
-        <v>10.543194275</v>
+        <v>10.50747845</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09168498750992657</v>
+        <v>0.09209858934434091</v>
       </c>
       <c r="T15">
-        <v>0.8943838122508087</v>
+        <v>0.9024456818402337</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>7.381989528559013</v>
+        <v>6.854704562233368</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2688,22 +2688,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08490628683613317</v>
+        <v>0.08475238453863024</v>
       </c>
       <c r="C16">
-        <v>69.9121910007463</v>
+        <v>69.32583000870079</v>
       </c>
       <c r="D16">
-        <v>73.5601910007463</v>
+        <v>73.8508300087008</v>
       </c>
       <c r="E16">
-        <v>-21.122</v>
+        <v>-20.245</v>
       </c>
       <c r="F16">
-        <v>12.278</v>
+        <v>13.155</v>
       </c>
       <c r="G16">
         <v>8.630000000000001</v>
@@ -2724,28 +2724,28 @@
         <v>4.57</v>
       </c>
       <c r="M16">
-        <v>0.6666953999999999</v>
+        <v>0.7143165</v>
       </c>
       <c r="N16">
-        <v>3.9033046</v>
+        <v>3.8556835</v>
       </c>
       <c r="O16">
-        <v>0.9758261500000001</v>
+        <v>0.9639208750000001</v>
       </c>
       <c r="P16">
-        <v>2.92747845</v>
+        <v>2.891762625</v>
       </c>
       <c r="Q16">
-        <v>10.50747845</v>
+        <v>10.471762625</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09209858934434091</v>
+        <v>0.09252192298662382</v>
       </c>
       <c r="T16">
-        <v>0.9024456818402337</v>
+        <v>0.9106972424788216</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>6.854704562233368</v>
+        <v>6.397724258084477</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2770,22 +2770,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08475238453863024</v>
+        <v>0.08471848224112731</v>
       </c>
       <c r="C17">
-        <v>69.32583000870079</v>
+        <v>68.51316224021694</v>
       </c>
       <c r="D17">
-        <v>73.8508300087008</v>
+        <v>73.91516224021694</v>
       </c>
       <c r="E17">
-        <v>-20.245</v>
+        <v>-19.368</v>
       </c>
       <c r="F17">
-        <v>13.155</v>
+        <v>14.032</v>
       </c>
       <c r="G17">
         <v>8.630000000000001</v>
@@ -2806,45 +2806,45 @@
         <v>4.57</v>
       </c>
       <c r="M17">
-        <v>0.7143164999999999</v>
+        <v>0.7759695999999999</v>
       </c>
       <c r="N17">
-        <v>3.8556835</v>
+        <v>3.7940304</v>
       </c>
       <c r="O17">
-        <v>0.9639208750000001</v>
+        <v>0.9485076000000001</v>
       </c>
       <c r="P17">
-        <v>2.891762625</v>
+        <v>2.8455228</v>
       </c>
       <c r="Q17">
-        <v>10.471762625</v>
+        <v>10.4255228</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09252192298662382</v>
+        <v>0.09295533600134204</v>
       </c>
       <c r="T17">
-        <v>0.9106972424788216</v>
+        <v>0.9191452688468997</v>
       </c>
       <c r="U17">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y17">
-        <v>6.397724258084478</v>
+        <v>5.889405976728987</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2852,22 +2852,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08471848224112731</v>
+        <v>0.08457207994362438</v>
       </c>
       <c r="C18">
-        <v>68.51316224021694</v>
+        <v>67.91526384085338</v>
       </c>
       <c r="D18">
-        <v>73.91516224021694</v>
+        <v>74.19426384085338</v>
       </c>
       <c r="E18">
-        <v>-19.368</v>
+        <v>-18.491</v>
       </c>
       <c r="F18">
-        <v>14.032</v>
+        <v>14.909</v>
       </c>
       <c r="G18">
         <v>8.630000000000001</v>
@@ -2888,28 +2888,28 @@
         <v>4.57</v>
       </c>
       <c r="M18">
-        <v>0.7759695999999999</v>
+        <v>0.8244676999999999</v>
       </c>
       <c r="N18">
-        <v>3.7940304</v>
+        <v>3.7455323</v>
       </c>
       <c r="O18">
-        <v>0.9485076000000001</v>
+        <v>0.9363830750000001</v>
       </c>
       <c r="P18">
-        <v>2.8455228</v>
+        <v>2.809149225</v>
       </c>
       <c r="Q18">
-        <v>10.4255228</v>
+        <v>10.389149225</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09295533600134204</v>
+        <v>0.09339919270316191</v>
       </c>
       <c r="T18">
-        <v>0.9191452688468997</v>
+        <v>0.9277968621154136</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.889405976728987</v>
+        <v>5.542970331039045</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2934,22 +2934,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08457207994362438</v>
+        <v>0.08442567764612144</v>
       </c>
       <c r="C19">
-        <v>67.91526384085338</v>
+        <v>67.31948119029011</v>
       </c>
       <c r="D19">
-        <v>74.19426384085338</v>
+        <v>74.47548119029011</v>
       </c>
       <c r="E19">
-        <v>-18.491</v>
+        <v>-17.614</v>
       </c>
       <c r="F19">
-        <v>14.909</v>
+        <v>15.786</v>
       </c>
       <c r="G19">
         <v>8.630000000000001</v>
@@ -2970,28 +2970,28 @@
         <v>4.57</v>
       </c>
       <c r="M19">
-        <v>0.8244676999999999</v>
+        <v>0.8729658</v>
       </c>
       <c r="N19">
-        <v>3.7455323</v>
+        <v>3.6970342</v>
       </c>
       <c r="O19">
-        <v>0.9363830750000001</v>
+        <v>0.92425855</v>
       </c>
       <c r="P19">
-        <v>2.809149225</v>
+        <v>2.77277565</v>
       </c>
       <c r="Q19">
-        <v>10.389149225</v>
+        <v>10.35277565</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09339919270316191</v>
+        <v>0.09385387517819688</v>
       </c>
       <c r="T19">
-        <v>0.9277968621154136</v>
+        <v>0.9366594698538909</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.542970331039045</v>
+        <v>5.235027534870209</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3016,22 +3016,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08442567764612144</v>
+        <v>0.08427927534861852</v>
       </c>
       <c r="C20">
-        <v>67.31948119029011</v>
+        <v>66.72583843792823</v>
       </c>
       <c r="D20">
-        <v>74.47548119029011</v>
+        <v>74.75883843792823</v>
       </c>
       <c r="E20">
-        <v>-17.614</v>
+        <v>-16.737</v>
       </c>
       <c r="F20">
-        <v>15.786</v>
+        <v>16.663</v>
       </c>
       <c r="G20">
         <v>8.630000000000001</v>
@@ -3052,28 +3052,28 @@
         <v>4.57</v>
       </c>
       <c r="M20">
-        <v>0.8729657999999999</v>
+        <v>0.9214638999999999</v>
       </c>
       <c r="N20">
-        <v>3.6970342</v>
+        <v>3.6485361</v>
       </c>
       <c r="O20">
-        <v>0.9242585500000001</v>
+        <v>0.9121340250000001</v>
       </c>
       <c r="P20">
-        <v>2.77277565</v>
+        <v>2.736402075</v>
       </c>
       <c r="Q20">
-        <v>10.35277565</v>
+        <v>10.316402075</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09385387517819688</v>
+        <v>0.0943197843810105</v>
       </c>
       <c r="T20">
-        <v>0.9366594698538909</v>
+        <v>0.9457409074130717</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.23502753487021</v>
+        <v>4.959499769877041</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3098,22 +3098,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08427927534861852</v>
+        <v>0.08413287305111557</v>
       </c>
       <c r="C21">
-        <v>66.72583843792823</v>
+        <v>66.13436010209804</v>
       </c>
       <c r="D21">
-        <v>74.75883843792823</v>
+        <v>75.04436010209805</v>
       </c>
       <c r="E21">
-        <v>-16.737</v>
+        <v>-15.86</v>
       </c>
       <c r="F21">
-        <v>16.663</v>
+        <v>17.54</v>
       </c>
       <c r="G21">
         <v>8.630000000000001</v>
@@ -3134,28 +3134,28 @@
         <v>4.57</v>
       </c>
       <c r="M21">
-        <v>0.9214638999999999</v>
+        <v>0.969962</v>
       </c>
       <c r="N21">
-        <v>3.6485361</v>
+        <v>3.600038000000001</v>
       </c>
       <c r="O21">
-        <v>0.9121340250000001</v>
+        <v>0.9000095000000001</v>
       </c>
       <c r="P21">
-        <v>2.736402075</v>
+        <v>2.7000285</v>
       </c>
       <c r="Q21">
-        <v>10.316402075</v>
+        <v>10.2800285</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.0943197843810105</v>
+        <v>0.09479734131389446</v>
       </c>
       <c r="T21">
-        <v>0.9457409074130717</v>
+        <v>0.9550493809112317</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>4.959499769877041</v>
+        <v>4.711524781383188</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3180,22 +3180,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08413287305111557</v>
+        <v>0.08438022075361264</v>
       </c>
       <c r="C22">
-        <v>66.13436010209804</v>
+        <v>64.77623143839338</v>
       </c>
       <c r="D22">
-        <v>75.04436010209805</v>
+        <v>74.56323143839339</v>
       </c>
       <c r="E22">
-        <v>-15.86</v>
+        <v>-14.983</v>
       </c>
       <c r="F22">
-        <v>17.54</v>
+        <v>18.417</v>
       </c>
       <c r="G22">
         <v>8.630000000000001</v>
@@ -3216,45 +3216,45 @@
         <v>4.57</v>
       </c>
       <c r="M22">
-        <v>0.969962</v>
+        <v>1.0645026</v>
       </c>
       <c r="N22">
-        <v>3.600038000000001</v>
+        <v>3.5054974</v>
       </c>
       <c r="O22">
-        <v>0.9000095000000001</v>
+        <v>0.8763743500000001</v>
       </c>
       <c r="P22">
-        <v>2.7000285</v>
+        <v>2.62912305</v>
       </c>
       <c r="Q22">
-        <v>10.2800285</v>
+        <v>10.20912305</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09479734131389446</v>
+        <v>0.09528698829571219</v>
       </c>
       <c r="T22">
-        <v>0.9550493809112317</v>
+        <v>0.9645935119663073</v>
       </c>
       <c r="U22">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y22">
-        <v>4.711524781383188</v>
+        <v>4.293084864236123</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3262,22 +3262,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08438022075361264</v>
+        <v>0.08425256845610971</v>
       </c>
       <c r="C23">
-        <v>64.77623143839338</v>
+        <v>64.14676153025755</v>
       </c>
       <c r="D23">
-        <v>74.56323143839339</v>
+        <v>74.81076153025755</v>
       </c>
       <c r="E23">
-        <v>-14.983</v>
+        <v>-14.106</v>
       </c>
       <c r="F23">
-        <v>18.417</v>
+        <v>19.294</v>
       </c>
       <c r="G23">
         <v>8.630000000000001</v>
@@ -3298,28 +3298,28 @@
         <v>4.57</v>
       </c>
       <c r="M23">
-        <v>1.0645026</v>
+        <v>1.1151932</v>
       </c>
       <c r="N23">
-        <v>3.5054974</v>
+        <v>3.4548068</v>
       </c>
       <c r="O23">
-        <v>0.8763743500000001</v>
+        <v>0.8637017</v>
       </c>
       <c r="P23">
-        <v>2.62912305</v>
+        <v>2.5911051</v>
       </c>
       <c r="Q23">
-        <v>10.20912305</v>
+        <v>10.1711051</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09528698829571219</v>
+        <v>0.09578919032834576</v>
       </c>
       <c r="T23">
-        <v>0.9645935119663073</v>
+        <v>0.9743823643304874</v>
       </c>
       <c r="U23">
         <v>0.0578</v>
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.293084864236123</v>
+        <v>4.097944643134481</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3344,22 +3344,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08425256845610971</v>
+        <v>0.08472866615860677</v>
       </c>
       <c r="C24">
-        <v>64.14676153025755</v>
+        <v>62.35482569501735</v>
       </c>
       <c r="D24">
-        <v>74.81076153025755</v>
+        <v>73.89582569501735</v>
       </c>
       <c r="E24">
-        <v>-14.106</v>
+        <v>-13.229</v>
       </c>
       <c r="F24">
-        <v>19.294</v>
+        <v>20.171</v>
       </c>
       <c r="G24">
         <v>8.630000000000001</v>
@@ -3380,45 +3380,45 @@
         <v>4.57</v>
       </c>
       <c r="M24">
-        <v>1.1151932</v>
+        <v>1.2364823</v>
       </c>
       <c r="N24">
-        <v>3.4548068</v>
+        <v>3.3335177</v>
       </c>
       <c r="O24">
-        <v>0.8637017</v>
+        <v>0.8333794250000001</v>
       </c>
       <c r="P24">
-        <v>2.5911051</v>
+        <v>2.500138275</v>
       </c>
       <c r="Q24">
-        <v>10.1711051</v>
+        <v>10.080138275</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09578919032834576</v>
+        <v>0.09630443656961918</v>
       </c>
       <c r="T24">
-        <v>0.9743823643304874</v>
+        <v>0.9844254726002307</v>
       </c>
       <c r="U24">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>4.097944643134481</v>
+        <v>3.695968797935886</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3426,22 +3426,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08472866615860677</v>
+        <v>0.08462726386110382</v>
       </c>
       <c r="C25">
-        <v>62.35482569501735</v>
+        <v>61.67081396553154</v>
       </c>
       <c r="D25">
-        <v>73.89582569501735</v>
+        <v>74.08881396553154</v>
       </c>
       <c r="E25">
-        <v>-13.229</v>
+        <v>-12.352</v>
       </c>
       <c r="F25">
-        <v>20.171</v>
+        <v>21.048</v>
       </c>
       <c r="G25">
         <v>8.630000000000001</v>
@@ -3462,28 +3462,28 @@
         <v>4.57</v>
       </c>
       <c r="M25">
-        <v>1.2364823</v>
+        <v>1.2902424</v>
       </c>
       <c r="N25">
-        <v>3.3335177</v>
+        <v>3.2797576</v>
       </c>
       <c r="O25">
-        <v>0.8333794250000001</v>
+        <v>0.8199394000000001</v>
       </c>
       <c r="P25">
-        <v>2.500138275</v>
+        <v>2.4598182</v>
       </c>
       <c r="Q25">
-        <v>10.080138275</v>
+        <v>10.0398182</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09630443656961918</v>
+        <v>0.09683324192250503</v>
       </c>
       <c r="T25">
-        <v>0.9844254726002307</v>
+        <v>0.994732873192862</v>
       </c>
       <c r="U25">
         <v>0.0613</v>
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.695968797935886</v>
+        <v>3.541970098021892</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3508,22 +3508,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08462726386110382</v>
+        <v>0.08505086156360089</v>
       </c>
       <c r="C26">
-        <v>61.67081396553154</v>
+        <v>59.99424294654439</v>
       </c>
       <c r="D26">
-        <v>74.08881396553154</v>
+        <v>73.28924294654439</v>
       </c>
       <c r="E26">
-        <v>-12.352</v>
+        <v>-11.475</v>
       </c>
       <c r="F26">
-        <v>21.048</v>
+        <v>21.925</v>
       </c>
       <c r="G26">
         <v>8.630000000000001</v>
@@ -3544,45 +3544,45 @@
         <v>4.57</v>
       </c>
       <c r="M26">
-        <v>1.2902424</v>
+        <v>1.4053925</v>
       </c>
       <c r="N26">
-        <v>3.2797576</v>
+        <v>3.164607500000001</v>
       </c>
       <c r="O26">
-        <v>0.8199394000000001</v>
+        <v>0.7911518750000002</v>
       </c>
       <c r="P26">
-        <v>2.4598182</v>
+        <v>2.373455625000001</v>
       </c>
       <c r="Q26">
-        <v>10.0398182</v>
+        <v>9.953455625</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09683324192250503</v>
+        <v>0.09737614875146786</v>
       </c>
       <c r="T26">
-        <v>0.994732873192862</v>
+        <v>1.005315137801297</v>
       </c>
       <c r="U26">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>3.541970098021892</v>
+        <v>3.251760629148086</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3590,22 +3590,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08505086156360089</v>
+        <v>0.08497045926609795</v>
       </c>
       <c r="C27">
-        <v>59.99424294654439</v>
+        <v>59.26767834162422</v>
       </c>
       <c r="D27">
-        <v>73.28924294654439</v>
+        <v>73.43967834162422</v>
       </c>
       <c r="E27">
-        <v>-11.475</v>
+        <v>-10.598</v>
       </c>
       <c r="F27">
-        <v>21.925</v>
+        <v>22.802</v>
       </c>
       <c r="G27">
         <v>8.630000000000001</v>
@@ -3626,28 +3626,28 @@
         <v>4.57</v>
       </c>
       <c r="M27">
-        <v>1.4053925</v>
+        <v>1.4616082</v>
       </c>
       <c r="N27">
-        <v>3.164607500000001</v>
+        <v>3.108391800000001</v>
       </c>
       <c r="O27">
-        <v>0.7911518750000002</v>
+        <v>0.7770979500000001</v>
       </c>
       <c r="P27">
-        <v>2.373455625000001</v>
+        <v>2.331293850000001</v>
       </c>
       <c r="Q27">
-        <v>9.953455625</v>
+        <v>9.91129385</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09737614875146786</v>
+        <v>0.09793372873797021</v>
       </c>
       <c r="T27">
-        <v>1.005315137801297</v>
+        <v>1.016183409561311</v>
       </c>
       <c r="U27">
         <v>0.0641</v>
@@ -3664,7 +3664,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.251760629148086</v>
+        <v>3.12669291264239</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3672,22 +3672,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08497045926609795</v>
+        <v>0.08489005696859502</v>
       </c>
       <c r="C28">
-        <v>59.26767834162422</v>
+        <v>58.54173258212549</v>
       </c>
       <c r="D28">
-        <v>73.43967834162422</v>
+        <v>73.5907325821255</v>
       </c>
       <c r="E28">
-        <v>-10.598</v>
+        <v>-9.721</v>
       </c>
       <c r="F28">
-        <v>22.802</v>
+        <v>23.679</v>
       </c>
       <c r="G28">
         <v>8.630000000000001</v>
@@ -3708,28 +3708,28 @@
         <v>4.57</v>
       </c>
       <c r="M28">
-        <v>1.4616082</v>
+        <v>1.5178239</v>
       </c>
       <c r="N28">
-        <v>3.108391800000001</v>
+        <v>3.052176100000001</v>
       </c>
       <c r="O28">
-        <v>0.7770979500000001</v>
+        <v>0.7630440250000001</v>
       </c>
       <c r="P28">
-        <v>2.331293850000001</v>
+        <v>2.289132075</v>
       </c>
       <c r="Q28">
-        <v>9.91129385</v>
+        <v>9.869132075</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09793372873797021</v>
+        <v>0.09850658488848633</v>
       </c>
       <c r="T28">
-        <v>1.016183409561311</v>
+        <v>1.027349442191462</v>
       </c>
       <c r="U28">
         <v>0.0641</v>
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.12669291264239</v>
+        <v>3.010889471433412</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3754,22 +3754,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08489005696859502</v>
+        <v>0.08644765467109208</v>
       </c>
       <c r="C29">
-        <v>58.54173258212549</v>
+        <v>54.84477268720654</v>
       </c>
       <c r="D29">
-        <v>73.5907325821255</v>
+        <v>70.77077268720655</v>
       </c>
       <c r="E29">
-        <v>-9.721</v>
+        <v>-8.844000000000001</v>
       </c>
       <c r="F29">
-        <v>23.679</v>
+        <v>24.556</v>
       </c>
       <c r="G29">
         <v>8.630000000000001</v>
@@ -3790,45 +3790,45 @@
         <v>4.57</v>
       </c>
       <c r="M29">
-        <v>1.5178239</v>
+        <v>1.7655764</v>
       </c>
       <c r="N29">
-        <v>3.052176100000001</v>
+        <v>2.8044236</v>
       </c>
       <c r="O29">
-        <v>0.7630440250000001</v>
+        <v>0.7011059000000001</v>
       </c>
       <c r="P29">
-        <v>2.289132075</v>
+        <v>2.1033177</v>
       </c>
       <c r="Q29">
-        <v>9.869132075</v>
+        <v>9.6833177</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09850658488848633</v>
+        <v>0.09909535370985012</v>
       </c>
       <c r="T29">
-        <v>1.027349442191462</v>
+        <v>1.038825642394673</v>
       </c>
       <c r="U29">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>3.010889471433412</v>
+        <v>2.588389831218858</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3836,22 +3836,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08644765467109208</v>
+        <v>0.08727400237358914</v>
       </c>
       <c r="C30">
-        <v>54.84477268720654</v>
+        <v>52.55770223181072</v>
       </c>
       <c r="D30">
-        <v>70.77077268720655</v>
+        <v>69.36070223181072</v>
       </c>
       <c r="E30">
-        <v>-8.844000000000001</v>
+        <v>-7.966999999999999</v>
       </c>
       <c r="F30">
-        <v>24.556</v>
+        <v>25.433</v>
       </c>
       <c r="G30">
         <v>8.630000000000001</v>
@@ -3872,45 +3872,45 @@
         <v>4.57</v>
       </c>
       <c r="M30">
-        <v>1.7655764</v>
+        <v>1.9278214</v>
       </c>
       <c r="N30">
-        <v>2.8044236</v>
+        <v>2.6421786</v>
       </c>
       <c r="O30">
-        <v>0.7011059000000001</v>
+        <v>0.6605446500000001</v>
       </c>
       <c r="P30">
-        <v>2.1033177</v>
+        <v>1.98163395</v>
       </c>
       <c r="Q30">
-        <v>9.6833177</v>
+        <v>9.561633950000001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09909535370985012</v>
+        <v>0.09970070756843541</v>
       </c>
       <c r="T30">
-        <v>1.038825642394673</v>
+        <v>1.050625115843045</v>
       </c>
       <c r="U30">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y30">
-        <v>2.588389831218858</v>
+        <v>2.370551545905653</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3918,22 +3918,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08727400237358914</v>
+        <v>0.0872813500760862</v>
       </c>
       <c r="C31">
-        <v>52.55770223181072</v>
+        <v>51.66841618509208</v>
       </c>
       <c r="D31">
-        <v>69.36070223181072</v>
+        <v>69.34841618509208</v>
       </c>
       <c r="E31">
-        <v>-7.967000000000002</v>
+        <v>-7.090000000000003</v>
       </c>
       <c r="F31">
-        <v>25.433</v>
+        <v>26.31</v>
       </c>
       <c r="G31">
         <v>8.630000000000001</v>
@@ -3954,28 +3954,28 @@
         <v>4.57</v>
       </c>
       <c r="M31">
-        <v>1.9278214</v>
+        <v>1.994298</v>
       </c>
       <c r="N31">
-        <v>2.6421786</v>
+        <v>2.575702000000001</v>
       </c>
       <c r="O31">
-        <v>0.6605446500000001</v>
+        <v>0.6439255000000002</v>
       </c>
       <c r="P31">
-        <v>1.98163395</v>
+        <v>1.9317765</v>
       </c>
       <c r="Q31">
-        <v>9.561633950000001</v>
+        <v>9.5117765</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09970070756843541</v>
+        <v>0.1003233572515517</v>
       </c>
       <c r="T31">
-        <v>1.050625115843045</v>
+        <v>1.062761717104228</v>
       </c>
       <c r="U31">
         <v>0.07580000000000001</v>
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.370551545905653</v>
+        <v>2.291533161042131</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4000,22 +4000,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0872813500760862</v>
+        <v>0.08728869777858328</v>
       </c>
       <c r="C32">
-        <v>51.66841618509208</v>
+        <v>50.77913449012323</v>
       </c>
       <c r="D32">
-        <v>69.34841618509208</v>
+        <v>69.33613449012323</v>
       </c>
       <c r="E32">
-        <v>-7.090000000000003</v>
+        <v>-6.213000000000001</v>
       </c>
       <c r="F32">
-        <v>26.31</v>
+        <v>27.187</v>
       </c>
       <c r="G32">
         <v>8.630000000000001</v>
@@ -4036,28 +4036,28 @@
         <v>4.57</v>
       </c>
       <c r="M32">
-        <v>1.994298</v>
+        <v>2.0607746</v>
       </c>
       <c r="N32">
-        <v>2.575702000000001</v>
+        <v>2.5092254</v>
       </c>
       <c r="O32">
-        <v>0.6439255000000002</v>
+        <v>0.6273063500000001</v>
       </c>
       <c r="P32">
-        <v>1.9317765</v>
+        <v>1.88191905</v>
       </c>
       <c r="Q32">
-        <v>9.5117765</v>
+        <v>9.461919050000001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1003233572515517</v>
+        <v>0.10096405475157</v>
       </c>
       <c r="T32">
-        <v>1.062761717104228</v>
+        <v>1.075250103909213</v>
       </c>
       <c r="U32">
         <v>0.07580000000000001</v>
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.291533161042131</v>
+        <v>2.217612736492385</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4082,22 +4082,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08728869777858328</v>
+        <v>0.08729604548108033</v>
       </c>
       <c r="C33">
-        <v>50.77913449012323</v>
+        <v>49.88985714459251</v>
       </c>
       <c r="D33">
-        <v>69.33613449012323</v>
+        <v>69.32385714459251</v>
       </c>
       <c r="E33">
-        <v>-6.213000000000001</v>
+        <v>-5.336000000000002</v>
       </c>
       <c r="F33">
-        <v>27.187</v>
+        <v>28.064</v>
       </c>
       <c r="G33">
         <v>8.630000000000001</v>
@@ -4118,28 +4118,28 @@
         <v>4.57</v>
       </c>
       <c r="M33">
-        <v>2.0607746</v>
+        <v>2.1272512</v>
       </c>
       <c r="N33">
-        <v>2.5092254</v>
+        <v>2.4427488</v>
       </c>
       <c r="O33">
-        <v>0.6273063500000001</v>
+        <v>0.6106872000000001</v>
       </c>
       <c r="P33">
-        <v>1.88191905</v>
+        <v>1.8320616</v>
       </c>
       <c r="Q33">
-        <v>9.461919050000001</v>
+        <v>9.412061600000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.10096405475157</v>
+        <v>0.1016235962957064</v>
       </c>
       <c r="T33">
-        <v>1.075250103909213</v>
+        <v>1.088105796208462</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4156,7 +4156,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.217612736492385</v>
+        <v>2.148312338476998</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4164,22 +4164,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08729604548108033</v>
+        <v>0.0873033931835774</v>
       </c>
       <c r="C34">
-        <v>49.88985714459251</v>
+        <v>49.00058414618984</v>
       </c>
       <c r="D34">
-        <v>69.32385714459251</v>
+        <v>69.31158414618984</v>
       </c>
       <c r="E34">
-        <v>-5.336000000000002</v>
+        <v>-4.459</v>
       </c>
       <c r="F34">
-        <v>28.064</v>
+        <v>28.941</v>
       </c>
       <c r="G34">
         <v>8.630000000000001</v>
@@ -4200,28 +4200,28 @@
         <v>4.57</v>
       </c>
       <c r="M34">
-        <v>2.1272512</v>
+        <v>2.1937278</v>
       </c>
       <c r="N34">
-        <v>2.4427488</v>
+        <v>2.3762722</v>
       </c>
       <c r="O34">
-        <v>0.6106872000000001</v>
+        <v>0.5940680500000001</v>
       </c>
       <c r="P34">
-        <v>1.8320616</v>
+        <v>1.78220415</v>
       </c>
       <c r="Q34">
-        <v>9.412061600000001</v>
+        <v>9.36220415</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1016235962957064</v>
+        <v>0.1023028256471305</v>
       </c>
       <c r="T34">
-        <v>1.088105796208462</v>
+        <v>1.101345240516644</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.148312338476998</v>
+        <v>2.083211964583755</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4246,22 +4246,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0873033931835774</v>
+        <v>0.08731074088607446</v>
       </c>
       <c r="C35">
-        <v>49.00058414618984</v>
+        <v>48.11131549260681</v>
       </c>
       <c r="D35">
-        <v>69.31158414618984</v>
+        <v>69.29931549260681</v>
       </c>
       <c r="E35">
-        <v>-4.459</v>
+        <v>-3.582000000000001</v>
       </c>
       <c r="F35">
-        <v>28.941</v>
+        <v>29.818</v>
       </c>
       <c r="G35">
         <v>8.630000000000001</v>
@@ -4282,28 +4282,28 @@
         <v>4.57</v>
       </c>
       <c r="M35">
-        <v>2.1937278</v>
+        <v>2.2602044</v>
       </c>
       <c r="N35">
-        <v>2.3762722</v>
+        <v>2.3097956</v>
       </c>
       <c r="O35">
-        <v>0.5940680500000001</v>
+        <v>0.5774489</v>
       </c>
       <c r="P35">
-        <v>1.78220415</v>
+        <v>1.7323467</v>
       </c>
       <c r="Q35">
-        <v>9.36220415</v>
+        <v>9.312346700000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1023028256471305</v>
+        <v>0.1030026377061734</v>
       </c>
       <c r="T35">
-        <v>1.101345240516644</v>
+        <v>1.114985880106893</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4320,7 +4320,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.083211964583755</v>
+        <v>2.021941024448939</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4328,22 +4328,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08731074088607446</v>
+        <v>0.09104558858857152</v>
       </c>
       <c r="C36">
-        <v>48.11131549260681</v>
+        <v>41.5139260065574</v>
       </c>
       <c r="D36">
-        <v>69.29931549260681</v>
+        <v>63.5789260065574</v>
       </c>
       <c r="E36">
-        <v>-3.582000000000001</v>
+        <v>-2.704999999999998</v>
       </c>
       <c r="F36">
-        <v>29.818</v>
+        <v>30.695</v>
       </c>
       <c r="G36">
         <v>8.630000000000001</v>
@@ -4364,45 +4364,45 @@
         <v>4.57</v>
       </c>
       <c r="M36">
-        <v>2.2602044</v>
+        <v>2.76255</v>
       </c>
       <c r="N36">
-        <v>2.3097956</v>
+        <v>1.80745</v>
       </c>
       <c r="O36">
-        <v>0.5774489</v>
+        <v>0.4518625000000001</v>
       </c>
       <c r="P36">
-        <v>1.7323467</v>
+        <v>1.3555875</v>
       </c>
       <c r="Q36">
-        <v>9.312346700000001</v>
+        <v>8.9355875</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1030026377061734</v>
+        <v>0.1037239824439562</v>
       </c>
       <c r="T36">
-        <v>1.114985880106893</v>
+        <v>1.129046231684533</v>
       </c>
       <c r="U36">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V36">
         <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>2.021941024448939</v>
+        <v>1.654268701018986</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4410,22 +4410,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09104558858857152</v>
+        <v>0.0911594362910686</v>
       </c>
       <c r="C37">
-        <v>41.5139260065574</v>
+        <v>40.47734918539432</v>
       </c>
       <c r="D37">
-        <v>63.5789260065574</v>
+        <v>63.41934918539432</v>
       </c>
       <c r="E37">
-        <v>-2.704999999999998</v>
+        <v>-1.827999999999999</v>
       </c>
       <c r="F37">
-        <v>30.695</v>
+        <v>31.572</v>
       </c>
       <c r="G37">
         <v>8.630000000000001</v>
@@ -4446,28 +4446,28 @@
         <v>4.57</v>
       </c>
       <c r="M37">
-        <v>2.76255</v>
+        <v>2.84148</v>
       </c>
       <c r="N37">
-        <v>1.80745</v>
+        <v>1.728520000000001</v>
       </c>
       <c r="O37">
-        <v>0.4518625000000001</v>
+        <v>0.4321300000000001</v>
       </c>
       <c r="P37">
-        <v>1.3555875</v>
+        <v>1.29639</v>
       </c>
       <c r="Q37">
-        <v>8.9355875</v>
+        <v>8.876390000000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1037239824439562</v>
+        <v>0.1044678692047947</v>
       </c>
       <c r="T37">
-        <v>1.129046231684533</v>
+        <v>1.143545969248975</v>
       </c>
       <c r="U37">
         <v>0.09</v>
@@ -4484,7 +4484,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>1.654268701018986</v>
+        <v>1.608316792657348</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4492,22 +4492,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.0911594362910686</v>
+        <v>0.09127328399356566</v>
       </c>
       <c r="C38">
-        <v>40.47734918539432</v>
+        <v>39.4415714028256</v>
       </c>
       <c r="D38">
-        <v>63.41934918539432</v>
+        <v>63.2605714028256</v>
       </c>
       <c r="E38">
-        <v>-1.828000000000003</v>
+        <v>-0.9510000000000005</v>
       </c>
       <c r="F38">
-        <v>31.572</v>
+        <v>32.449</v>
       </c>
       <c r="G38">
         <v>8.630000000000001</v>
@@ -4528,28 +4528,28 @@
         <v>4.57</v>
       </c>
       <c r="M38">
-        <v>2.841479999999999</v>
+        <v>2.92041</v>
       </c>
       <c r="N38">
-        <v>1.728520000000001</v>
+        <v>1.649590000000001</v>
       </c>
       <c r="O38">
-        <v>0.4321300000000002</v>
+        <v>0.4123975000000002</v>
       </c>
       <c r="P38">
-        <v>1.296390000000001</v>
+        <v>1.237192500000001</v>
       </c>
       <c r="Q38">
-        <v>8.876390000000001</v>
+        <v>8.817192500000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1044678692047947</v>
+        <v>0.1052353714183582</v>
       </c>
       <c r="T38">
-        <v>1.143545969248975</v>
+        <v>1.158506015942447</v>
       </c>
       <c r="U38">
         <v>0.09</v>
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>1.608316792657348</v>
+        <v>1.564848771234177</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4574,22 +4574,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09127328399356566</v>
+        <v>0.09138713169606273</v>
       </c>
       <c r="C39">
-        <v>39.4415714028256</v>
+        <v>38.4065866723784</v>
       </c>
       <c r="D39">
-        <v>63.2605714028256</v>
+        <v>63.10258667237839</v>
       </c>
       <c r="E39">
-        <v>-0.9510000000000005</v>
+        <v>-0.07400000000000517</v>
       </c>
       <c r="F39">
-        <v>32.449</v>
+        <v>33.32599999999999</v>
       </c>
       <c r="G39">
         <v>8.630000000000001</v>
@@ -4610,28 +4610,28 @@
         <v>4.57</v>
       </c>
       <c r="M39">
-        <v>2.92041</v>
+        <v>2.999339999999999</v>
       </c>
       <c r="N39">
-        <v>1.649590000000001</v>
+        <v>1.570660000000001</v>
       </c>
       <c r="O39">
-        <v>0.4123975000000002</v>
+        <v>0.3926650000000003</v>
       </c>
       <c r="P39">
-        <v>1.237192500000001</v>
+        <v>1.177995000000001</v>
       </c>
       <c r="Q39">
-        <v>8.817192500000001</v>
+        <v>8.757995000000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1052353714183582</v>
+        <v>0.1060276317678431</v>
       </c>
       <c r="T39">
-        <v>1.158506015942447</v>
+        <v>1.173948644787321</v>
       </c>
       <c r="U39">
         <v>0.09</v>
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>1.564848771234177</v>
+        <v>1.523668540412225</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4656,22 +4656,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09138713169606273</v>
+        <v>0.109761965145694</v>
       </c>
       <c r="C40">
-        <v>38.4065866723784</v>
+        <v>19.40163332221569</v>
       </c>
       <c r="D40">
-        <v>63.10258667237839</v>
+        <v>44.97463332221569</v>
       </c>
       <c r="E40">
-        <v>-0.07400000000000517</v>
+        <v>0.8029999999999973</v>
       </c>
       <c r="F40">
-        <v>33.32599999999999</v>
+        <v>34.203</v>
       </c>
       <c r="G40">
         <v>8.630000000000001</v>
@@ -4692,45 +4692,45 @@
         <v>4.57</v>
       </c>
       <c r="M40">
-        <v>2.999339999999999</v>
+        <v>5.0210004</v>
       </c>
       <c r="N40">
-        <v>1.570660000000001</v>
+        <v>-0.4510003999999999</v>
       </c>
       <c r="O40">
-        <v>0.3926650000000003</v>
+        <v>-0.1127501</v>
       </c>
       <c r="P40">
-        <v>1.177995000000001</v>
+        <v>-0.3382502999999999</v>
       </c>
       <c r="Q40">
-        <v>8.757995000000001</v>
+        <v>7.2417497</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1060276317678431</v>
+        <v>0.1074382478134729</v>
       </c>
       <c r="T40">
-        <v>1.173948644787321</v>
+        <v>1.20144417709491</v>
       </c>
       <c r="U40">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V40">
-        <v>0.25</v>
+        <v>0.2275442957542883</v>
       </c>
       <c r="W40">
-        <v>0.0675</v>
+        <v>0.1133964973832705</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y40">
-        <v>1.523668540412225</v>
+        <v>0.9101771830171533</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4738,22 +4738,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.109761965145694</v>
+        <v>0.110771965145694</v>
       </c>
       <c r="C41">
-        <v>19.40163332221569</v>
+        <v>17.82549517003608</v>
       </c>
       <c r="D41">
-        <v>44.97463332221569</v>
+        <v>44.27549517003608</v>
       </c>
       <c r="E41">
-        <v>0.8029999999999973</v>
+        <v>1.68</v>
       </c>
       <c r="F41">
-        <v>34.203</v>
+        <v>35.08</v>
       </c>
       <c r="G41">
         <v>8.630000000000001</v>
@@ -4774,37 +4774,37 @@
         <v>4.57</v>
       </c>
       <c r="M41">
-        <v>5.0210004</v>
+        <v>5.149744</v>
       </c>
       <c r="N41">
-        <v>-0.4510003999999999</v>
+        <v>-0.5797439999999998</v>
       </c>
       <c r="O41">
-        <v>-0.1127501</v>
+        <v>-0.144936</v>
       </c>
       <c r="P41">
-        <v>-0.3382502999999999</v>
+        <v>-0.4348079999999999</v>
       </c>
       <c r="Q41">
-        <v>7.2417497</v>
+        <v>7.145192</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1074382478134729</v>
+        <v>0.1084655519436975</v>
       </c>
       <c r="T41">
-        <v>1.20144417709491</v>
+        <v>1.221468246713159</v>
       </c>
       <c r="U41">
         <v>0.1468</v>
       </c>
       <c r="V41">
-        <v>0.2275442957542883</v>
+        <v>0.2218556883604311</v>
       </c>
       <c r="W41">
-        <v>0.1133964973832705</v>
+        <v>0.1142315849486887</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.9101771830171533</v>
+        <v>0.8874227534417245</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4820,22 +4820,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.110771965145694</v>
+        <v>0.111781965145694</v>
       </c>
       <c r="C42">
-        <v>17.82549517003608</v>
+        <v>16.27076073119368</v>
       </c>
       <c r="D42">
-        <v>44.27549517003608</v>
+        <v>43.59776073119368</v>
       </c>
       <c r="E42">
-        <v>1.68</v>
+        <v>2.557000000000002</v>
       </c>
       <c r="F42">
-        <v>35.08</v>
+        <v>35.957</v>
       </c>
       <c r="G42">
         <v>8.630000000000001</v>
@@ -4856,37 +4856,37 @@
         <v>4.57</v>
       </c>
       <c r="M42">
-        <v>5.149744</v>
+        <v>5.278487600000001</v>
       </c>
       <c r="N42">
-        <v>-0.5797439999999998</v>
+        <v>-0.7084876000000007</v>
       </c>
       <c r="O42">
-        <v>-0.144936</v>
+        <v>-0.1771219000000002</v>
       </c>
       <c r="P42">
-        <v>-0.4348079999999999</v>
+        <v>-0.5313657000000005</v>
       </c>
       <c r="Q42">
-        <v>7.145192</v>
+        <v>7.0486343</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1084655519436975</v>
+        <v>0.1095276799427432</v>
       </c>
       <c r="T42">
-        <v>1.221468246713159</v>
+        <v>1.242171098352365</v>
       </c>
       <c r="U42">
         <v>0.1468</v>
       </c>
       <c r="V42">
-        <v>0.2218556883604311</v>
+        <v>0.2164445740101767</v>
       </c>
       <c r="W42">
-        <v>0.1142315849486887</v>
+        <v>0.1150259365353061</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.8874227534417245</v>
+        <v>0.8657782960407068</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4902,22 +4902,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.111781965145694</v>
+        <v>0.112791965145694</v>
       </c>
       <c r="C43">
-        <v>16.27076073119368</v>
+        <v>14.73646193061753</v>
       </c>
       <c r="D43">
-        <v>43.59776073119368</v>
+        <v>42.94046193061752</v>
       </c>
       <c r="E43">
-        <v>2.557000000000002</v>
+        <v>3.433999999999997</v>
       </c>
       <c r="F43">
-        <v>35.957</v>
+        <v>36.834</v>
       </c>
       <c r="G43">
         <v>8.630000000000001</v>
@@ -4938,37 +4938,37 @@
         <v>4.57</v>
       </c>
       <c r="M43">
-        <v>5.278487600000001</v>
+        <v>5.4072312</v>
       </c>
       <c r="N43">
-        <v>-0.7084876000000007</v>
+        <v>-0.8372311999999997</v>
       </c>
       <c r="O43">
-        <v>-0.1771219000000002</v>
+        <v>-0.2093077999999999</v>
       </c>
       <c r="P43">
-        <v>-0.5313657000000005</v>
+        <v>-0.6279233999999998</v>
       </c>
       <c r="Q43">
-        <v>7.0486343</v>
+        <v>6.9520766</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1095276799427432</v>
+        <v>0.1106264330452043</v>
       </c>
       <c r="T43">
-        <v>1.242171098352365</v>
+        <v>1.263587841427406</v>
       </c>
       <c r="U43">
         <v>0.1468</v>
       </c>
       <c r="V43">
-        <v>0.2164445740101767</v>
+        <v>0.2112911317718392</v>
       </c>
       <c r="W43">
-        <v>0.1150259365353061</v>
+        <v>0.115782461855894</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.8657782960407068</v>
+        <v>0.8451645270873567</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4984,22 +4984,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.112791965145694</v>
+        <v>0.113801965145694</v>
       </c>
       <c r="C44">
-        <v>14.73646193061752</v>
+        <v>13.22168820662284</v>
       </c>
       <c r="D44">
-        <v>42.94046193061751</v>
+        <v>42.30268820662283</v>
       </c>
       <c r="E44">
-        <v>3.433999999999997</v>
+        <v>4.310999999999993</v>
       </c>
       <c r="F44">
-        <v>36.834</v>
+        <v>37.71099999999999</v>
       </c>
       <c r="G44">
         <v>8.630000000000001</v>
@@ -5020,37 +5020,37 @@
         <v>4.57</v>
       </c>
       <c r="M44">
-        <v>5.4072312</v>
+        <v>5.535974799999999</v>
       </c>
       <c r="N44">
-        <v>-0.8372311999999997</v>
+        <v>-0.9659747999999988</v>
       </c>
       <c r="O44">
-        <v>-0.2093077999999999</v>
+        <v>-0.2414936999999997</v>
       </c>
       <c r="P44">
-        <v>-0.6279233999999998</v>
+        <v>-0.7244810999999991</v>
       </c>
       <c r="Q44">
-        <v>6.9520766</v>
+        <v>6.855518900000001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1106264330452043</v>
+        <v>0.1117637388881026</v>
       </c>
       <c r="T44">
-        <v>1.263587841427406</v>
+        <v>1.285756049171746</v>
       </c>
       <c r="U44">
         <v>0.1468</v>
       </c>
       <c r="V44">
-        <v>0.2112911317718392</v>
+        <v>0.2063773845213313</v>
       </c>
       <c r="W44">
-        <v>0.115782461855894</v>
+        <v>0.1165037999522686</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.8451645270873567</v>
+        <v>0.8255095380853252</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5066,22 +5066,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.113801965145694</v>
+        <v>0.114811965145694</v>
       </c>
       <c r="C45">
-        <v>13.22168820662284</v>
+        <v>11.72558230232801</v>
       </c>
       <c r="D45">
-        <v>42.30268820662283</v>
+        <v>41.68358230232801</v>
       </c>
       <c r="E45">
-        <v>4.310999999999993</v>
+        <v>5.187999999999995</v>
       </c>
       <c r="F45">
-        <v>37.71099999999999</v>
+        <v>38.58799999999999</v>
       </c>
       <c r="G45">
         <v>8.630000000000001</v>
@@ -5102,37 +5102,37 @@
         <v>4.57</v>
       </c>
       <c r="M45">
-        <v>5.535974799999999</v>
+        <v>5.6647184</v>
       </c>
       <c r="N45">
-        <v>-0.9659747999999988</v>
+        <v>-1.0947184</v>
       </c>
       <c r="O45">
-        <v>-0.2414936999999997</v>
+        <v>-0.2736795999999999</v>
       </c>
       <c r="P45">
-        <v>-0.7244810999999991</v>
+        <v>-0.8210387999999997</v>
       </c>
       <c r="Q45">
-        <v>6.855518900000001</v>
+        <v>6.7589612</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1117637388881026</v>
+        <v>0.1129416627968187</v>
       </c>
       <c r="T45">
-        <v>1.285756049171746</v>
+        <v>1.308715978621242</v>
       </c>
       <c r="U45">
         <v>0.1468</v>
       </c>
       <c r="V45">
-        <v>0.2063773845213313</v>
+        <v>0.2016869894185738</v>
       </c>
       <c r="W45">
-        <v>0.1165037999522686</v>
+        <v>0.1171923499533534</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.8255095380853252</v>
+        <v>0.8067479576742951</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5148,22 +5148,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.114811965145694</v>
+        <v>0.1411066551013096</v>
       </c>
       <c r="C46">
-        <v>11.72558230232801</v>
+        <v>-0.6517360302586184</v>
       </c>
       <c r="D46">
-        <v>41.68358230232801</v>
+        <v>30.18326396974138</v>
       </c>
       <c r="E46">
-        <v>5.187999999999995</v>
+        <v>6.064999999999998</v>
       </c>
       <c r="F46">
-        <v>38.58799999999999</v>
+        <v>39.465</v>
       </c>
       <c r="G46">
         <v>8.630000000000001</v>
@@ -5184,45 +5184,45 @@
         <v>4.57</v>
       </c>
       <c r="M46">
-        <v>5.6647184</v>
+        <v>7.924572</v>
       </c>
       <c r="N46">
-        <v>-1.0947184</v>
+        <v>-3.354571999999999</v>
       </c>
       <c r="O46">
-        <v>-0.2736795999999999</v>
+        <v>-0.8386429999999998</v>
       </c>
       <c r="P46">
-        <v>-0.8210387999999997</v>
+        <v>-2.515928999999999</v>
       </c>
       <c r="Q46">
-        <v>6.7589612</v>
+        <v>5.064071</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1129416627968187</v>
+        <v>0.115952765676062</v>
       </c>
       <c r="T46">
-        <v>1.308715978621242</v>
+        <v>1.367407978300535</v>
       </c>
       <c r="U46">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.2016869894185738</v>
+        <v>0.1441718240429893</v>
       </c>
       <c r="W46">
-        <v>0.1171923499533534</v>
+        <v>0.1718502977321678</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y46">
-        <v>0.8067479576742951</v>
+        <v>0.5766872961719574</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5230,22 +5230,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1411066551013096</v>
+        <v>0.1426566551013096</v>
       </c>
       <c r="C47">
-        <v>-0.6517360302586184</v>
+        <v>-2.011759722375217</v>
       </c>
       <c r="D47">
-        <v>30.18326396974138</v>
+        <v>29.70024027762478</v>
       </c>
       <c r="E47">
-        <v>6.064999999999998</v>
+        <v>6.942</v>
       </c>
       <c r="F47">
-        <v>39.465</v>
+        <v>40.342</v>
       </c>
       <c r="G47">
         <v>8.630000000000001</v>
@@ -5266,37 +5266,37 @@
         <v>4.57</v>
       </c>
       <c r="M47">
-        <v>7.924572</v>
+        <v>8.1006736</v>
       </c>
       <c r="N47">
-        <v>-3.354571999999999</v>
+        <v>-3.5306736</v>
       </c>
       <c r="O47">
-        <v>-0.8386429999999998</v>
+        <v>-0.8826684</v>
       </c>
       <c r="P47">
-        <v>-2.515928999999999</v>
+        <v>-2.6480052</v>
       </c>
       <c r="Q47">
-        <v>5.064071</v>
+        <v>4.9319948</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.115952765676062</v>
+        <v>0.1172518909663594</v>
       </c>
       <c r="T47">
-        <v>1.367407978300535</v>
+        <v>1.392730348269063</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.1441718240429893</v>
+        <v>0.1410376539550983</v>
       </c>
       <c r="W47">
-        <v>0.1718502977321678</v>
+        <v>0.1724796390858163</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.5766872961719574</v>
+        <v>0.5641506158203931</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5312,22 +5312,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1426566551013096</v>
+        <v>0.1442066551013096</v>
       </c>
       <c r="C48">
-        <v>-2.011759722375217</v>
+        <v>-3.356567233797335</v>
       </c>
       <c r="D48">
-        <v>29.70024027762478</v>
+        <v>29.23243276620266</v>
       </c>
       <c r="E48">
-        <v>6.942</v>
+        <v>7.818999999999996</v>
       </c>
       <c r="F48">
-        <v>40.342</v>
+        <v>41.21899999999999</v>
       </c>
       <c r="G48">
         <v>8.630000000000001</v>
@@ -5348,37 +5348,37 @@
         <v>4.57</v>
       </c>
       <c r="M48">
-        <v>8.1006736</v>
+        <v>8.276775199999999</v>
       </c>
       <c r="N48">
-        <v>-3.5306736</v>
+        <v>-3.706775199999999</v>
       </c>
       <c r="O48">
-        <v>-0.8826684</v>
+        <v>-0.9266937999999998</v>
       </c>
       <c r="P48">
-        <v>-2.6480052</v>
+        <v>-2.780081399999999</v>
       </c>
       <c r="Q48">
-        <v>4.9319948</v>
+        <v>4.799918600000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1172518909663594</v>
+        <v>0.1186000398525171</v>
       </c>
       <c r="T48">
-        <v>1.392730348269063</v>
+        <v>1.419008279368479</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.1410376539550983</v>
+        <v>0.1380368528071174</v>
       </c>
       <c r="W48">
-        <v>0.1724796390858163</v>
+        <v>0.1730821999563308</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.5641506158203931</v>
+        <v>0.5521474112284699</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5394,22 +5394,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1442066551013096</v>
+        <v>0.1457566551013096</v>
       </c>
       <c r="C49">
-        <v>-3.356567233797335</v>
+        <v>-4.686866423748121</v>
       </c>
       <c r="D49">
-        <v>29.23243276620266</v>
+        <v>28.77913357625187</v>
       </c>
       <c r="E49">
-        <v>7.818999999999996</v>
+        <v>8.695999999999998</v>
       </c>
       <c r="F49">
-        <v>41.21899999999999</v>
+        <v>42.096</v>
       </c>
       <c r="G49">
         <v>8.630000000000001</v>
@@ -5430,37 +5430,37 @@
         <v>4.57</v>
       </c>
       <c r="M49">
-        <v>8.276775199999999</v>
+        <v>8.4528768</v>
       </c>
       <c r="N49">
-        <v>-3.706775199999999</v>
+        <v>-3.8828768</v>
       </c>
       <c r="O49">
-        <v>-0.9266937999999998</v>
+        <v>-0.9707192</v>
       </c>
       <c r="P49">
-        <v>-2.780081399999999</v>
+        <v>-2.9121576</v>
       </c>
       <c r="Q49">
-        <v>4.799918600000001</v>
+        <v>4.6678424</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1186000398525171</v>
+        <v>0.1200000406189117</v>
       </c>
       <c r="T49">
-        <v>1.419008279368479</v>
+        <v>1.446296900125566</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.1380368528071174</v>
+        <v>0.1351610850403025</v>
       </c>
       <c r="W49">
-        <v>0.1730821999563308</v>
+        <v>0.1736596541239073</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.5521474112284699</v>
+        <v>0.54064434016121</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5476,22 +5476,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1457566551013096</v>
+        <v>0.1473066551013096</v>
       </c>
       <c r="C50">
-        <v>-4.686866423748121</v>
+        <v>-6.003321915594142</v>
       </c>
       <c r="D50">
-        <v>28.77913357625187</v>
+        <v>28.33967808440585</v>
       </c>
       <c r="E50">
-        <v>8.695999999999998</v>
+        <v>9.572999999999993</v>
       </c>
       <c r="F50">
-        <v>42.096</v>
+        <v>42.97299999999999</v>
       </c>
       <c r="G50">
         <v>8.630000000000001</v>
@@ -5512,37 +5512,37 @@
         <v>4.57</v>
       </c>
       <c r="M50">
-        <v>8.4528768</v>
+        <v>8.628978399999999</v>
       </c>
       <c r="N50">
-        <v>-3.8828768</v>
+        <v>-4.058978399999999</v>
       </c>
       <c r="O50">
-        <v>-0.9707192</v>
+        <v>-1.0147446</v>
       </c>
       <c r="P50">
-        <v>-2.9121576</v>
+        <v>-3.044233799999999</v>
       </c>
       <c r="Q50">
-        <v>4.6678424</v>
+        <v>4.535766200000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1200000406189117</v>
+        <v>0.1214549433761453</v>
       </c>
       <c r="T50">
-        <v>1.446296900125565</v>
+        <v>1.474655662873126</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.1351610850403025</v>
+        <v>0.1324026955496841</v>
       </c>
       <c r="W50">
-        <v>0.1736596541239073</v>
+        <v>0.1742135387336234</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.54064434016121</v>
+        <v>0.5296107821987364</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5558,22 +5558,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1473066551013096</v>
+        <v>0.1488566551013096</v>
       </c>
       <c r="C51">
-        <v>-6.003321915594142</v>
+        <v>-7.306558348240316</v>
       </c>
       <c r="D51">
-        <v>28.33967808440585</v>
+        <v>27.91344165175968</v>
       </c>
       <c r="E51">
-        <v>9.572999999999993</v>
+        <v>10.45</v>
       </c>
       <c r="F51">
-        <v>42.97299999999999</v>
+        <v>43.84999999999999</v>
       </c>
       <c r="G51">
         <v>8.630000000000001</v>
@@ -5594,37 +5594,37 @@
         <v>4.57</v>
       </c>
       <c r="M51">
-        <v>8.628978399999999</v>
+        <v>8.805079999999998</v>
       </c>
       <c r="N51">
-        <v>-4.058978399999999</v>
+        <v>-4.235079999999998</v>
       </c>
       <c r="O51">
-        <v>-1.0147446</v>
+        <v>-1.05877</v>
       </c>
       <c r="P51">
-        <v>-3.044233799999999</v>
+        <v>-3.176309999999999</v>
       </c>
       <c r="Q51">
-        <v>4.535766200000001</v>
+        <v>4.403690000000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1214549433761453</v>
+        <v>0.1229680422436682</v>
       </c>
       <c r="T51">
-        <v>1.474655662873126</v>
+        <v>1.504148776130588</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.1324026955496841</v>
+        <v>0.1297546416386904</v>
       </c>
       <c r="W51">
-        <v>0.1742135387336234</v>
+        <v>0.174745267958951</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.5296107821987364</v>
+        <v>0.5190185665547618</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5640,22 +5640,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1488566551013096</v>
+        <v>0.1504066551013096</v>
       </c>
       <c r="C52">
-        <v>-7.306558348240316</v>
+        <v>-8.5971633384613</v>
       </c>
       <c r="D52">
-        <v>27.91344165175968</v>
+        <v>27.49983666153869</v>
       </c>
       <c r="E52">
-        <v>10.45</v>
+        <v>11.327</v>
       </c>
       <c r="F52">
-        <v>43.84999999999999</v>
+        <v>44.727</v>
       </c>
       <c r="G52">
         <v>8.630000000000001</v>
@@ -5676,37 +5676,37 @@
         <v>4.57</v>
       </c>
       <c r="M52">
-        <v>8.805079999999998</v>
+        <v>8.981181599999999</v>
       </c>
       <c r="N52">
-        <v>-4.235079999999998</v>
+        <v>-4.411181599999999</v>
       </c>
       <c r="O52">
-        <v>-1.05877</v>
+        <v>-1.1027954</v>
       </c>
       <c r="P52">
-        <v>-3.176309999999999</v>
+        <v>-3.308386199999999</v>
       </c>
       <c r="Q52">
-        <v>4.403690000000001</v>
+        <v>4.271613800000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1229680422436682</v>
+        <v>0.124542900248641</v>
       </c>
       <c r="T52">
-        <v>1.504148776130588</v>
+        <v>1.534845689929172</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.1297546416386904</v>
+        <v>0.1272104329791083</v>
       </c>
       <c r="W52">
-        <v>0.174745267958951</v>
+        <v>0.1752561450577951</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.5190185665547618</v>
+        <v>0.508841731916433</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5722,22 +5722,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1504066551013096</v>
+        <v>0.1705539893921362</v>
       </c>
       <c r="C53">
-        <v>-8.5971633384613</v>
+        <v>-13.91529107203318</v>
       </c>
       <c r="D53">
-        <v>27.49983666153869</v>
+        <v>23.05870892796681</v>
       </c>
       <c r="E53">
-        <v>11.327</v>
+        <v>12.20399999999999</v>
       </c>
       <c r="F53">
-        <v>44.727</v>
+        <v>45.60399999999999</v>
       </c>
       <c r="G53">
         <v>8.630000000000001</v>
@@ -5758,45 +5758,45 @@
         <v>4.57</v>
       </c>
       <c r="M53">
-        <v>8.981181599999999</v>
+        <v>10.7534232</v>
       </c>
       <c r="N53">
-        <v>-4.411181599999999</v>
+        <v>-6.183423199999998</v>
       </c>
       <c r="O53">
-        <v>-1.1027954</v>
+        <v>-1.5458558</v>
       </c>
       <c r="P53">
-        <v>-3.308386199999999</v>
+        <v>-4.637567399999998</v>
       </c>
       <c r="Q53">
-        <v>4.271613800000001</v>
+        <v>2.942432600000002</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.124542900248641</v>
+        <v>0.1270111571097097</v>
       </c>
       <c r="T53">
-        <v>1.534845689929172</v>
+        <v>1.582956610315481</v>
       </c>
       <c r="U53">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.1272104329791083</v>
+        <v>0.1062452373305647</v>
       </c>
       <c r="W53">
-        <v>0.1752561450577951</v>
+        <v>0.2107473730374529</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y53">
-        <v>0.508841731916433</v>
+        <v>0.4249809493222587</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5804,22 +5804,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1705539893921362</v>
+        <v>0.1724539893921362</v>
       </c>
       <c r="C54">
-        <v>-13.91529107203318</v>
+        <v>-15.13820632644725</v>
       </c>
       <c r="D54">
-        <v>23.05870892796681</v>
+        <v>22.71279367355275</v>
       </c>
       <c r="E54">
-        <v>12.20399999999999</v>
+        <v>13.081</v>
       </c>
       <c r="F54">
-        <v>45.60399999999999</v>
+        <v>46.48099999999999</v>
       </c>
       <c r="G54">
         <v>8.630000000000001</v>
@@ -5840,37 +5840,37 @@
         <v>4.57</v>
       </c>
       <c r="M54">
-        <v>10.7534232</v>
+        <v>10.9602198</v>
       </c>
       <c r="N54">
-        <v>-6.183423199999998</v>
+        <v>-6.390219799999999</v>
       </c>
       <c r="O54">
-        <v>-1.5458558</v>
+        <v>-1.59755495</v>
       </c>
       <c r="P54">
-        <v>-4.637567399999998</v>
+        <v>-4.79266485</v>
       </c>
       <c r="Q54">
-        <v>2.942432600000002</v>
+        <v>2.787335150000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1270111571097097</v>
+        <v>0.1287390540694908</v>
       </c>
       <c r="T54">
-        <v>1.582956610315481</v>
+        <v>1.616636538194534</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.1062452373305647</v>
+        <v>0.10424061021112</v>
       </c>
       <c r="W54">
-        <v>0.2107473730374529</v>
+        <v>0.2112200641122179</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.4249809493222587</v>
+        <v>0.4169624408444802</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5886,22 +5886,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1724539893921362</v>
+        <v>0.1743539893921361</v>
       </c>
       <c r="C55">
-        <v>-15.13820632644725</v>
+        <v>-16.35089647642862</v>
       </c>
       <c r="D55">
-        <v>22.71279367355275</v>
+        <v>22.37710352357137</v>
       </c>
       <c r="E55">
-        <v>13.081</v>
+        <v>13.958</v>
       </c>
       <c r="F55">
-        <v>46.48099999999999</v>
+        <v>47.358</v>
       </c>
       <c r="G55">
         <v>8.630000000000001</v>
@@ -5922,37 +5922,37 @@
         <v>4.57</v>
       </c>
       <c r="M55">
-        <v>10.9602198</v>
+        <v>11.1670164</v>
       </c>
       <c r="N55">
-        <v>-6.390219799999999</v>
+        <v>-6.597016399999999</v>
       </c>
       <c r="O55">
-        <v>-1.59755495</v>
+        <v>-1.6492541</v>
       </c>
       <c r="P55">
-        <v>-4.79266485</v>
+        <v>-4.947762299999999</v>
       </c>
       <c r="Q55">
-        <v>2.787335150000001</v>
+        <v>2.632237700000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1287390540694908</v>
+        <v>0.1305420769840449</v>
       </c>
       <c r="T55">
-        <v>1.616636538194534</v>
+        <v>1.65178081076398</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.10424061021112</v>
+        <v>0.1023102285405438</v>
       </c>
       <c r="W55">
-        <v>0.2112200641122179</v>
+        <v>0.2116752481101398</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.4169624408444802</v>
+        <v>0.409240914162175</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5968,22 +5968,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1743539893921361</v>
+        <v>0.1762539893921362</v>
       </c>
       <c r="C56">
-        <v>-16.35089647642862</v>
+        <v>-17.55380829325305</v>
       </c>
       <c r="D56">
-        <v>22.37710352357137</v>
+        <v>22.05119170674695</v>
       </c>
       <c r="E56">
-        <v>13.958</v>
+        <v>14.835</v>
       </c>
       <c r="F56">
-        <v>47.358</v>
+        <v>48.235</v>
       </c>
       <c r="G56">
         <v>8.630000000000001</v>
@@ -6004,37 +6004,37 @@
         <v>4.57</v>
       </c>
       <c r="M56">
-        <v>11.1670164</v>
+        <v>11.373813</v>
       </c>
       <c r="N56">
-        <v>-6.597016399999999</v>
+        <v>-6.803813</v>
       </c>
       <c r="O56">
-        <v>-1.6492541</v>
+        <v>-1.70095325</v>
       </c>
       <c r="P56">
-        <v>-4.947762299999999</v>
+        <v>-5.10285975</v>
       </c>
       <c r="Q56">
-        <v>2.632237700000001</v>
+        <v>2.47714025</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1305420769840449</v>
+        <v>0.132425234250357</v>
       </c>
       <c r="T56">
-        <v>1.65178081076398</v>
+        <v>1.688487051003179</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.1023102285405438</v>
+        <v>0.1004500425670793</v>
       </c>
       <c r="W56">
-        <v>0.2116752481101398</v>
+        <v>0.2121138799626827</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.409240914162175</v>
+        <v>0.4018001702683173</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6050,22 +6050,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1762539893921362</v>
+        <v>0.1781539893921361</v>
       </c>
       <c r="C57">
-        <v>-17.55380829325305</v>
+        <v>-18.74736289379997</v>
       </c>
       <c r="D57">
-        <v>22.05119170674695</v>
+        <v>21.73463710620002</v>
       </c>
       <c r="E57">
-        <v>14.835</v>
+        <v>15.712</v>
       </c>
       <c r="F57">
-        <v>48.235</v>
+        <v>49.11199999999999</v>
       </c>
       <c r="G57">
         <v>8.630000000000001</v>
@@ -6086,37 +6086,37 @@
         <v>4.57</v>
       </c>
       <c r="M57">
-        <v>11.373813</v>
+        <v>11.5806096</v>
       </c>
       <c r="N57">
-        <v>-6.803813</v>
+        <v>-7.010609599999999</v>
       </c>
       <c r="O57">
-        <v>-1.70095325</v>
+        <v>-1.7526524</v>
       </c>
       <c r="P57">
-        <v>-5.10285975</v>
+        <v>-5.257957199999999</v>
       </c>
       <c r="Q57">
-        <v>2.47714025</v>
+        <v>2.322042800000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.132425234250357</v>
+        <v>0.1343939895742288</v>
       </c>
       <c r="T57">
-        <v>1.688487051003179</v>
+        <v>1.726861756707797</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.1004500425670793</v>
+        <v>0.0986562918069529</v>
       </c>
       <c r="W57">
-        <v>0.2121138799626827</v>
+        <v>0.2125368463919205</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.4018001702683173</v>
+        <v>0.3946251672278116</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6132,22 +6132,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1781539893921361</v>
+        <v>0.1800539893921362</v>
       </c>
       <c r="C58">
-        <v>-18.74736289379997</v>
+        <v>-19.93195755589349</v>
       </c>
       <c r="D58">
-        <v>21.73463710620002</v>
+        <v>21.4270424441065</v>
       </c>
       <c r="E58">
-        <v>15.712</v>
+        <v>16.589</v>
       </c>
       <c r="F58">
-        <v>49.11199999999999</v>
+        <v>49.989</v>
       </c>
       <c r="G58">
         <v>8.630000000000001</v>
@@ -6168,37 +6168,37 @@
         <v>4.57</v>
       </c>
       <c r="M58">
-        <v>11.5806096</v>
+        <v>11.7874062</v>
       </c>
       <c r="N58">
-        <v>-7.010609599999999</v>
+        <v>-7.217406199999999</v>
       </c>
       <c r="O58">
-        <v>-1.7526524</v>
+        <v>-1.80435155</v>
       </c>
       <c r="P58">
-        <v>-5.257957199999999</v>
+        <v>-5.413054649999999</v>
       </c>
       <c r="Q58">
-        <v>2.322042800000001</v>
+        <v>2.166945350000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1343939895742288</v>
+        <v>0.1364543149131643</v>
       </c>
       <c r="T58">
-        <v>1.726861756707797</v>
+        <v>1.767021332445188</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.0986562918069529</v>
+        <v>0.09692547966998881</v>
       </c>
       <c r="W58">
-        <v>0.2125368463919205</v>
+        <v>0.2129449718938167</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3946251672278116</v>
+        <v>0.3877019186799553</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6214,22 +6214,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1800539893921362</v>
+        <v>0.1819539893921362</v>
       </c>
       <c r="C59">
-        <v>-19.93195755589349</v>
+        <v>-21.10796738164711</v>
       </c>
       <c r="D59">
-        <v>21.4270424441065</v>
+        <v>21.12803261835289</v>
       </c>
       <c r="E59">
-        <v>16.589</v>
+        <v>17.466</v>
       </c>
       <c r="F59">
-        <v>49.989</v>
+        <v>50.866</v>
       </c>
       <c r="G59">
         <v>8.630000000000001</v>
@@ -6250,37 +6250,37 @@
         <v>4.57</v>
       </c>
       <c r="M59">
-        <v>11.7874062</v>
+        <v>11.9942028</v>
       </c>
       <c r="N59">
-        <v>-7.217406199999999</v>
+        <v>-7.4242028</v>
       </c>
       <c r="O59">
-        <v>-1.80435155</v>
+        <v>-1.8560507</v>
       </c>
       <c r="P59">
-        <v>-5.413054649999999</v>
+        <v>-5.5681521</v>
       </c>
       <c r="Q59">
-        <v>2.166945350000001</v>
+        <v>2.0118479</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1364543149131643</v>
+        <v>0.1386127509825254</v>
       </c>
       <c r="T59">
-        <v>1.767021332445188</v>
+        <v>1.809093268931978</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.09692547966998881</v>
+        <v>0.09525435071016142</v>
       </c>
       <c r="W59">
-        <v>0.2129449718938167</v>
+        <v>0.2133390241025439</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3877019186799553</v>
+        <v>0.3810174028406457</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6296,22 +6296,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1819539893921361</v>
+        <v>0.1838539893921362</v>
       </c>
       <c r="C60">
-        <v>-21.1079673816471</v>
+        <v>-22.27574682345551</v>
       </c>
       <c r="D60">
-        <v>21.12803261835289</v>
+        <v>20.83725317654448</v>
       </c>
       <c r="E60">
-        <v>17.46599999999999</v>
+        <v>18.34299999999999</v>
       </c>
       <c r="F60">
-        <v>50.86599999999999</v>
+        <v>51.74299999999999</v>
       </c>
       <c r="G60">
         <v>8.630000000000001</v>
@@ -6332,37 +6332,37 @@
         <v>4.57</v>
       </c>
       <c r="M60">
-        <v>11.9942028</v>
+        <v>12.2009994</v>
       </c>
       <c r="N60">
-        <v>-7.424202799999998</v>
+        <v>-7.630999399999997</v>
       </c>
       <c r="O60">
-        <v>-1.856050699999999</v>
+        <v>-1.907749849999999</v>
       </c>
       <c r="P60">
-        <v>-5.568152099999999</v>
+        <v>-5.723249549999998</v>
       </c>
       <c r="Q60">
-        <v>2.011847900000001</v>
+        <v>1.856750450000002</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1386127509825253</v>
+        <v>0.1408764766162455</v>
       </c>
       <c r="T60">
-        <v>1.809093268931977</v>
+        <v>1.853217495003489</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.09525435071016143</v>
+        <v>0.09363987018965023</v>
       </c>
       <c r="W60">
-        <v>0.2133390241025439</v>
+        <v>0.2137197186092805</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3810174028406458</v>
+        <v>0.3745594807586009</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6378,22 +6378,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1838539893921362</v>
+        <v>0.1857539893921361</v>
       </c>
       <c r="C61">
-        <v>-22.27574682345551</v>
+        <v>-23.43563108568619</v>
       </c>
       <c r="D61">
-        <v>20.83725317654448</v>
+        <v>20.5543689143138</v>
       </c>
       <c r="E61">
-        <v>18.34299999999999</v>
+        <v>19.21999999999999</v>
       </c>
       <c r="F61">
-        <v>51.74299999999999</v>
+        <v>52.61999999999999</v>
       </c>
       <c r="G61">
         <v>8.630000000000001</v>
@@ -6414,37 +6414,37 @@
         <v>4.57</v>
       </c>
       <c r="M61">
-        <v>12.2009994</v>
+        <v>12.407796</v>
       </c>
       <c r="N61">
-        <v>-7.630999399999997</v>
+        <v>-7.837795999999997</v>
       </c>
       <c r="O61">
-        <v>-1.907749849999999</v>
+        <v>-1.959448999999999</v>
       </c>
       <c r="P61">
-        <v>-5.723249549999998</v>
+        <v>-5.878346999999998</v>
       </c>
       <c r="Q61">
-        <v>1.856750450000002</v>
+        <v>1.701653000000002</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1408764766162455</v>
+        <v>0.1432533885316516</v>
       </c>
       <c r="T61">
-        <v>1.853217495003489</v>
+        <v>1.899547932378577</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.09363987018965023</v>
+        <v>0.09207920568648939</v>
       </c>
       <c r="W61">
-        <v>0.2137197186092805</v>
+        <v>0.2140877232991258</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3745594807586009</v>
+        <v>0.3683168227459576</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6460,22 +6460,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1857539893921361</v>
+        <v>0.1876539893921362</v>
       </c>
       <c r="C62">
-        <v>-23.43563108568619</v>
+        <v>-24.58793741372494</v>
       </c>
       <c r="D62">
-        <v>20.5543689143138</v>
+        <v>20.27906258627505</v>
       </c>
       <c r="E62">
-        <v>19.21999999999999</v>
+        <v>20.09699999999999</v>
       </c>
       <c r="F62">
-        <v>52.61999999999999</v>
+        <v>53.49699999999999</v>
       </c>
       <c r="G62">
         <v>8.630000000000001</v>
@@ -6496,37 +6496,37 @@
         <v>4.57</v>
       </c>
       <c r="M62">
-        <v>12.407796</v>
+        <v>12.6145926</v>
       </c>
       <c r="N62">
-        <v>-7.837795999999997</v>
+        <v>-8.044592599999998</v>
       </c>
       <c r="O62">
-        <v>-1.959448999999999</v>
+        <v>-2.011148149999999</v>
       </c>
       <c r="P62">
-        <v>-5.878346999999998</v>
+        <v>-6.033444449999998</v>
       </c>
       <c r="Q62">
-        <v>1.701653000000002</v>
+        <v>1.546555550000002</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1432533885316516</v>
+        <v>0.1457521933657966</v>
       </c>
       <c r="T62">
-        <v>1.899547932378577</v>
+        <v>1.948254289619053</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.09207920568648939</v>
+        <v>0.09056971051130103</v>
       </c>
       <c r="W62">
-        <v>0.2140877232991258</v>
+        <v>0.2144436622614352</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3683168227459576</v>
+        <v>0.3622788420452041</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6542,22 +6542,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1876539893921362</v>
+        <v>0.1895539893921361</v>
       </c>
       <c r="C63">
-        <v>-24.58793741372494</v>
+        <v>-25.73296628079741</v>
       </c>
       <c r="D63">
-        <v>20.27906258627505</v>
+        <v>20.01103371920258</v>
       </c>
       <c r="E63">
-        <v>20.09699999999999</v>
+        <v>20.974</v>
       </c>
       <c r="F63">
-        <v>53.49699999999999</v>
+        <v>54.374</v>
       </c>
       <c r="G63">
         <v>8.630000000000001</v>
@@ -6578,37 +6578,37 @@
         <v>4.57</v>
       </c>
       <c r="M63">
-        <v>12.6145926</v>
+        <v>12.8213892</v>
       </c>
       <c r="N63">
-        <v>-8.044592599999998</v>
+        <v>-8.251389199999998</v>
       </c>
       <c r="O63">
-        <v>-2.011148149999999</v>
+        <v>-2.0628473</v>
       </c>
       <c r="P63">
-        <v>-6.033444449999998</v>
+        <v>-6.188541899999999</v>
       </c>
       <c r="Q63">
-        <v>1.546555550000002</v>
+        <v>1.391458100000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1457521933657966</v>
+        <v>0.1483825142438438</v>
       </c>
       <c r="T63">
-        <v>1.948254289619053</v>
+        <v>1.99952413934587</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.09056971051130103</v>
+        <v>0.08910890872886069</v>
       </c>
       <c r="W63">
-        <v>0.2144436622614352</v>
+        <v>0.2147881193217347</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3622788420452041</v>
+        <v>0.3564356349154427</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6624,22 +6624,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1895539893921361</v>
+        <v>0.1914539893921361</v>
       </c>
       <c r="C64">
-        <v>-25.73296628079741</v>
+        <v>-26.87100248190085</v>
       </c>
       <c r="D64">
-        <v>20.01103371920258</v>
+        <v>19.74999751809914</v>
       </c>
       <c r="E64">
-        <v>20.974</v>
+        <v>21.85099999999999</v>
       </c>
       <c r="F64">
-        <v>54.374</v>
+        <v>55.25099999999999</v>
       </c>
       <c r="G64">
         <v>8.630000000000001</v>
@@ -6660,37 +6660,37 @@
         <v>4.57</v>
       </c>
       <c r="M64">
-        <v>12.8213892</v>
+        <v>13.0281858</v>
       </c>
       <c r="N64">
-        <v>-8.251389199999998</v>
+        <v>-8.458185799999997</v>
       </c>
       <c r="O64">
-        <v>-2.0628473</v>
+        <v>-2.114546449999999</v>
       </c>
       <c r="P64">
-        <v>-6.188541899999999</v>
+        <v>-6.343639349999998</v>
       </c>
       <c r="Q64">
-        <v>1.391458100000001</v>
+        <v>1.236360650000002</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1483825142438438</v>
+        <v>0.1511550146288126</v>
       </c>
       <c r="T64">
-        <v>1.99952413934587</v>
+        <v>2.053565332301164</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.08910890872886069</v>
+        <v>0.08769448160618037</v>
       </c>
       <c r="W64">
-        <v>0.2147881193217347</v>
+        <v>0.2151216412372627</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3564356349154427</v>
+        <v>0.3507779264247215</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6706,22 +6706,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1914539893921361</v>
+        <v>0.1933539893921361</v>
       </c>
       <c r="C65">
-        <v>-26.87100248190085</v>
+        <v>-28.00231614321883</v>
       </c>
       <c r="D65">
-        <v>19.74999751809914</v>
+        <v>19.49568385678116</v>
       </c>
       <c r="E65">
-        <v>21.85099999999999</v>
+        <v>22.72799999999999</v>
       </c>
       <c r="F65">
-        <v>55.25099999999999</v>
+        <v>56.12799999999999</v>
       </c>
       <c r="G65">
         <v>8.630000000000001</v>
@@ -6742,37 +6742,37 @@
         <v>4.57</v>
       </c>
       <c r="M65">
-        <v>13.0281858</v>
+        <v>13.2349824</v>
       </c>
       <c r="N65">
-        <v>-8.458185799999997</v>
+        <v>-8.664982399999998</v>
       </c>
       <c r="O65">
-        <v>-2.114546449999999</v>
+        <v>-2.166245599999999</v>
       </c>
       <c r="P65">
-        <v>-6.343639349999998</v>
+        <v>-6.498736799999998</v>
       </c>
       <c r="Q65">
-        <v>1.236360650000002</v>
+        <v>1.081263200000002</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1511550146288126</v>
+        <v>0.1540815428129463</v>
       </c>
       <c r="T65">
-        <v>2.053565332301164</v>
+        <v>2.110608813753974</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.08769448160618037</v>
+        <v>0.0863242553310838</v>
       </c>
       <c r="W65">
-        <v>0.2151216412372627</v>
+        <v>0.2154447405929305</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3507779264247215</v>
+        <v>0.3452970213243352</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6788,22 +6788,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1933539893921361</v>
+        <v>0.1952539893921361</v>
       </c>
       <c r="C66">
-        <v>-28.00231614321883</v>
+        <v>-29.12716365454015</v>
       </c>
       <c r="D66">
-        <v>19.49568385678116</v>
+        <v>19.24783634545984</v>
       </c>
       <c r="E66">
-        <v>22.72799999999999</v>
+        <v>23.605</v>
       </c>
       <c r="F66">
-        <v>56.12799999999999</v>
+        <v>57.005</v>
       </c>
       <c r="G66">
         <v>8.630000000000001</v>
@@ -6824,37 +6824,37 @@
         <v>4.57</v>
       </c>
       <c r="M66">
-        <v>13.2349824</v>
+        <v>13.441779</v>
       </c>
       <c r="N66">
-        <v>-8.664982399999998</v>
+        <v>-8.871778999999998</v>
       </c>
       <c r="O66">
-        <v>-2.166245599999999</v>
+        <v>-2.21794475</v>
       </c>
       <c r="P66">
-        <v>-6.498736799999998</v>
+        <v>-6.653834249999999</v>
       </c>
       <c r="Q66">
-        <v>1.081263200000002</v>
+        <v>0.9261657500000009</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1540815428129463</v>
+        <v>0.1571753011790304</v>
       </c>
       <c r="T66">
-        <v>2.110608813753974</v>
+        <v>2.170911922718374</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.0863242553310838</v>
+        <v>0.08499618986445173</v>
       </c>
       <c r="W66">
-        <v>0.2154447405929305</v>
+        <v>0.2157578984299623</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3452970213243352</v>
+        <v>0.3399847594578069</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6870,22 +6870,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1952539893921361</v>
+        <v>0.1971539893921362</v>
       </c>
       <c r="C67">
-        <v>-29.12716365454015</v>
+        <v>-30.24578853144794</v>
       </c>
       <c r="D67">
-        <v>19.24783634545984</v>
+        <v>19.00621146855206</v>
       </c>
       <c r="E67">
-        <v>23.605</v>
+        <v>24.482</v>
       </c>
       <c r="F67">
-        <v>57.005</v>
+        <v>57.882</v>
       </c>
       <c r="G67">
         <v>8.630000000000001</v>
@@ -6906,37 +6906,37 @@
         <v>4.57</v>
       </c>
       <c r="M67">
-        <v>13.441779</v>
+        <v>13.6485756</v>
       </c>
       <c r="N67">
-        <v>-8.871778999999998</v>
+        <v>-9.078575600000001</v>
       </c>
       <c r="O67">
-        <v>-2.21794475</v>
+        <v>-2.2696439</v>
       </c>
       <c r="P67">
-        <v>-6.653834249999999</v>
+        <v>-6.8089317</v>
       </c>
       <c r="Q67">
-        <v>0.9261657500000009</v>
+        <v>0.7710682999999996</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1571753011790304</v>
+        <v>0.1604510453313549</v>
       </c>
       <c r="T67">
-        <v>2.170911922718374</v>
+        <v>2.234762273386561</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.08499618986445173</v>
+        <v>0.08370836880589942</v>
       </c>
       <c r="W67">
-        <v>0.2157578984299623</v>
+        <v>0.2160615666355689</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3399847594578069</v>
+        <v>0.3348334752235977</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6952,22 +6952,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1971539893921362</v>
+        <v>0.1990539893921361</v>
       </c>
       <c r="C68">
-        <v>-30.24578853144794</v>
+        <v>-31.35842221337348</v>
       </c>
       <c r="D68">
-        <v>19.00621146855206</v>
+        <v>18.77057778662651</v>
       </c>
       <c r="E68">
-        <v>24.482</v>
+        <v>25.35899999999999</v>
       </c>
       <c r="F68">
-        <v>57.882</v>
+        <v>58.75899999999999</v>
       </c>
       <c r="G68">
         <v>8.630000000000001</v>
@@ -6988,37 +6988,37 @@
         <v>4.57</v>
       </c>
       <c r="M68">
-        <v>13.6485756</v>
+        <v>13.8553722</v>
       </c>
       <c r="N68">
-        <v>-9.078575600000001</v>
+        <v>-9.285372199999999</v>
       </c>
       <c r="O68">
-        <v>-2.2696439</v>
+        <v>-2.32134305</v>
       </c>
       <c r="P68">
-        <v>-6.8089317</v>
+        <v>-6.96402915</v>
       </c>
       <c r="Q68">
-        <v>0.7710682999999996</v>
+        <v>0.6159708500000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1604510453313549</v>
+        <v>0.163925319432305</v>
       </c>
       <c r="T68">
-        <v>2.234762273386561</v>
+        <v>2.302482342277063</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.08370836880589942</v>
+        <v>0.08245899016700541</v>
       </c>
       <c r="W68">
-        <v>0.2160615666355689</v>
+        <v>0.2163561701186201</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3348334752235977</v>
+        <v>0.3298359606680217</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7034,22 +7034,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1990539893921361</v>
+        <v>0.2009539893921362</v>
       </c>
       <c r="C69">
-        <v>-31.35842221337348</v>
+        <v>-32.46528480301308</v>
       </c>
       <c r="D69">
-        <v>18.77057778662651</v>
+        <v>18.54071519698692</v>
       </c>
       <c r="E69">
-        <v>25.35899999999999</v>
+        <v>26.236</v>
       </c>
       <c r="F69">
-        <v>58.75899999999999</v>
+        <v>59.636</v>
       </c>
       <c r="G69">
         <v>8.630000000000001</v>
@@ -7070,37 +7070,37 @@
         <v>4.57</v>
       </c>
       <c r="M69">
-        <v>13.8553722</v>
+        <v>14.0621688</v>
       </c>
       <c r="N69">
-        <v>-9.285372199999999</v>
+        <v>-9.4921688</v>
       </c>
       <c r="O69">
-        <v>-2.32134305</v>
+        <v>-2.3730422</v>
       </c>
       <c r="P69">
-        <v>-6.96402915</v>
+        <v>-7.1191266</v>
       </c>
       <c r="Q69">
-        <v>0.6159708500000001</v>
+        <v>0.4608734000000005</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.163925319432305</v>
+        <v>0.1676167356645646</v>
       </c>
       <c r="T69">
-        <v>2.302482342277063</v>
+        <v>2.374434915473221</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.08245899016700541</v>
+        <v>0.0812463579586671</v>
       </c>
       <c r="W69">
-        <v>0.2163561701186201</v>
+        <v>0.2166421087933463</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3298359606680217</v>
+        <v>0.3249854318346683</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7116,22 +7116,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2009539893921362</v>
+        <v>0.2028539893921362</v>
       </c>
       <c r="C70">
-        <v>-32.46528480301308</v>
+        <v>-33.56658575207282</v>
       </c>
       <c r="D70">
-        <v>18.54071519698692</v>
+        <v>18.31641424792718</v>
       </c>
       <c r="E70">
-        <v>26.236</v>
+        <v>27.113</v>
       </c>
       <c r="F70">
-        <v>59.636</v>
+        <v>60.513</v>
       </c>
       <c r="G70">
         <v>8.630000000000001</v>
@@ -7152,37 +7152,37 @@
         <v>4.57</v>
       </c>
       <c r="M70">
-        <v>14.0621688</v>
+        <v>14.2689654</v>
       </c>
       <c r="N70">
-        <v>-9.4921688</v>
+        <v>-9.698965400000001</v>
       </c>
       <c r="O70">
-        <v>-2.3730422</v>
+        <v>-2.42474135</v>
       </c>
       <c r="P70">
-        <v>-7.1191266</v>
+        <v>-7.274224050000001</v>
       </c>
       <c r="Q70">
-        <v>0.4608734000000005</v>
+        <v>0.3057759499999992</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1676167356645646</v>
+        <v>0.1715463077827764</v>
       </c>
       <c r="T70">
-        <v>2.374434915473221</v>
+        <v>2.451029590165906</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.0812463579586671</v>
+        <v>0.08006887450999076</v>
       </c>
       <c r="W70">
-        <v>0.2166421087933463</v>
+        <v>0.2169197593905442</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3249854318346683</v>
+        <v>0.320275498039963</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7198,22 +7198,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2028539893921362</v>
+        <v>0.2047539893921362</v>
       </c>
       <c r="C71">
-        <v>-33.56658575207282</v>
+        <v>-34.66252449783282</v>
       </c>
       <c r="D71">
-        <v>18.31641424792718</v>
+        <v>18.09747550216718</v>
       </c>
       <c r="E71">
-        <v>27.113</v>
+        <v>27.99</v>
       </c>
       <c r="F71">
-        <v>60.513</v>
+        <v>61.39</v>
       </c>
       <c r="G71">
         <v>8.630000000000001</v>
@@ -7234,37 +7234,37 @@
         <v>4.57</v>
       </c>
       <c r="M71">
-        <v>14.2689654</v>
+        <v>14.475762</v>
       </c>
       <c r="N71">
-        <v>-9.698965400000001</v>
+        <v>-9.905762000000001</v>
       </c>
       <c r="O71">
-        <v>-2.42474135</v>
+        <v>-2.4764405</v>
       </c>
       <c r="P71">
-        <v>-7.274224050000001</v>
+        <v>-7.4293215</v>
       </c>
       <c r="Q71">
-        <v>0.3057759499999992</v>
+        <v>0.1506784999999997</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1715463077827764</v>
+        <v>0.1757378513755356</v>
       </c>
       <c r="T71">
-        <v>2.451029590165906</v>
+        <v>2.53273057650477</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.08006887450999076</v>
+        <v>0.07892503344556231</v>
       </c>
       <c r="W71">
-        <v>0.2169197593905442</v>
+        <v>0.2171894771135364</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.320275498039963</v>
+        <v>0.3157001337822493</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7280,22 +7280,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2047539893921362</v>
+        <v>0.2066539893921362</v>
       </c>
       <c r="C72">
-        <v>-34.66252449783282</v>
+        <v>-35.75329105459686</v>
       </c>
       <c r="D72">
-        <v>18.09747550216718</v>
+        <v>17.88370894540313</v>
       </c>
       <c r="E72">
-        <v>27.99</v>
+        <v>28.867</v>
       </c>
       <c r="F72">
-        <v>61.39</v>
+        <v>62.267</v>
       </c>
       <c r="G72">
         <v>8.630000000000001</v>
@@ -7316,37 +7316,37 @@
         <v>4.57</v>
       </c>
       <c r="M72">
-        <v>14.475762</v>
+        <v>14.6825586</v>
       </c>
       <c r="N72">
-        <v>-9.905762000000001</v>
+        <v>-10.1125586</v>
       </c>
       <c r="O72">
-        <v>-2.4764405</v>
+        <v>-2.52813965</v>
       </c>
       <c r="P72">
-        <v>-7.4293215</v>
+        <v>-7.58441895</v>
       </c>
       <c r="Q72">
-        <v>0.1506784999999997</v>
+        <v>-0.004418949999999811</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1757378513755356</v>
+        <v>0.1802184669402092</v>
       </c>
       <c r="T72">
-        <v>2.53273057650477</v>
+        <v>2.620066113625624</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.07892503344556231</v>
+        <v>0.07781341325618819</v>
       </c>
       <c r="W72">
-        <v>0.2171894771135364</v>
+        <v>0.2174515971541908</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3157001337822493</v>
+        <v>0.3112536530247528</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7362,22 +7362,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2066539893921361</v>
+        <v>0.2085539893921362</v>
       </c>
       <c r="C73">
-        <v>-35.75329105459685</v>
+        <v>-36.83906656371447</v>
       </c>
       <c r="D73">
-        <v>17.88370894540314</v>
+        <v>17.67493343628552</v>
       </c>
       <c r="E73">
-        <v>28.86699999999999</v>
+        <v>29.74399999999999</v>
       </c>
       <c r="F73">
-        <v>62.26699999999999</v>
+        <v>63.14399999999999</v>
       </c>
       <c r="G73">
         <v>8.630000000000001</v>
@@ -7398,37 +7398,37 @@
         <v>4.57</v>
       </c>
       <c r="M73">
-        <v>14.6825586</v>
+        <v>14.8893552</v>
       </c>
       <c r="N73">
-        <v>-10.1125586</v>
+        <v>-10.3193552</v>
       </c>
       <c r="O73">
-        <v>-2.52813965</v>
+        <v>-2.5798388</v>
       </c>
       <c r="P73">
-        <v>-7.584418949999998</v>
+        <v>-7.739516399999999</v>
       </c>
       <c r="Q73">
-        <v>-0.004418949999998034</v>
+        <v>-0.1595163999999993</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1802184669402092</v>
+        <v>0.1850191264737881</v>
       </c>
       <c r="T73">
-        <v>2.620066113625623</v>
+        <v>2.713639903397967</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.07781341325618821</v>
+        <v>0.07673267140540782</v>
       </c>
       <c r="W73">
-        <v>0.2174515971541908</v>
+        <v>0.2177064360826048</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3112536530247528</v>
+        <v>0.3069306856216313</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7444,22 +7444,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2085539893921362</v>
+        <v>0.2104539893921362</v>
       </c>
       <c r="C74">
-        <v>-36.83906656371447</v>
+        <v>-37.92002380552149</v>
       </c>
       <c r="D74">
-        <v>17.67493343628552</v>
+        <v>17.4709761944785</v>
       </c>
       <c r="E74">
-        <v>29.74399999999999</v>
+        <v>30.62099999999999</v>
       </c>
       <c r="F74">
-        <v>63.14399999999999</v>
+        <v>64.02099999999999</v>
       </c>
       <c r="G74">
         <v>8.630000000000001</v>
@@ -7480,37 +7480,37 @@
         <v>4.57</v>
       </c>
       <c r="M74">
-        <v>14.8893552</v>
+        <v>15.0961518</v>
       </c>
       <c r="N74">
-        <v>-10.3193552</v>
+        <v>-10.5261518</v>
       </c>
       <c r="O74">
-        <v>-2.5798388</v>
+        <v>-2.631537949999999</v>
       </c>
       <c r="P74">
-        <v>-7.739516399999999</v>
+        <v>-7.894613849999998</v>
       </c>
       <c r="Q74">
-        <v>-0.1595163999999993</v>
+        <v>-0.314613849999998</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1850191264737881</v>
+        <v>0.1901753904172617</v>
       </c>
       <c r="T74">
-        <v>2.713639903397967</v>
+        <v>2.814145085005299</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.07673267140540782</v>
+        <v>0.07568153892040223</v>
       </c>
       <c r="W74">
-        <v>0.2177064360826048</v>
+        <v>0.2179542931225692</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3069306856216313</v>
+        <v>0.302726155681609</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7526,22 +7526,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2104539893921362</v>
+        <v>0.2123539893921361</v>
       </c>
       <c r="C75">
-        <v>-37.92002380552149</v>
+        <v>-38.99632767624028</v>
       </c>
       <c r="D75">
-        <v>17.4709761944785</v>
+        <v>17.27167232375971</v>
       </c>
       <c r="E75">
-        <v>30.62099999999999</v>
+        <v>31.498</v>
       </c>
       <c r="F75">
-        <v>64.02099999999999</v>
+        <v>64.898</v>
       </c>
       <c r="G75">
         <v>8.630000000000001</v>
@@ -7562,37 +7562,37 @@
         <v>4.57</v>
       </c>
       <c r="M75">
-        <v>15.0961518</v>
+        <v>15.3029484</v>
       </c>
       <c r="N75">
-        <v>-10.5261518</v>
+        <v>-10.7329484</v>
       </c>
       <c r="O75">
-        <v>-2.631537949999999</v>
+        <v>-2.6832371</v>
       </c>
       <c r="P75">
-        <v>-7.894613849999998</v>
+        <v>-8.0497113</v>
       </c>
       <c r="Q75">
-        <v>-0.314613849999998</v>
+        <v>-0.4697113000000002</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1901753904172617</v>
+        <v>0.1957282900486949</v>
       </c>
       <c r="T75">
-        <v>2.814145085005299</v>
+        <v>2.922381434428579</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.07568153892040223</v>
+        <v>0.07465881542147787</v>
       </c>
       <c r="W75">
-        <v>0.2179542931225692</v>
+        <v>0.2181954513236155</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.302726155681609</v>
+        <v>0.2986352616859115</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7608,22 +7608,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2123539893921361</v>
+        <v>0.2142539893921362</v>
       </c>
       <c r="C76">
-        <v>-38.99632767624028</v>
+        <v>-40.06813563260606</v>
       </c>
       <c r="D76">
-        <v>17.27167232375971</v>
+        <v>17.07686436739393</v>
       </c>
       <c r="E76">
-        <v>31.498</v>
+        <v>32.37499999999999</v>
       </c>
       <c r="F76">
-        <v>64.898</v>
+        <v>65.77499999999999</v>
       </c>
       <c r="G76">
         <v>8.630000000000001</v>
@@ -7644,37 +7644,37 @@
         <v>4.57</v>
       </c>
       <c r="M76">
-        <v>15.3029484</v>
+        <v>15.509745</v>
       </c>
       <c r="N76">
-        <v>-10.7329484</v>
+        <v>-10.939745</v>
       </c>
       <c r="O76">
-        <v>-2.6832371</v>
+        <v>-2.73493625</v>
       </c>
       <c r="P76">
-        <v>-8.0497113</v>
+        <v>-8.204808749999998</v>
       </c>
       <c r="Q76">
-        <v>-0.4697113000000002</v>
+        <v>-0.6248087499999979</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1957282900486949</v>
+        <v>0.2017254216506426</v>
       </c>
       <c r="T76">
-        <v>2.922381434428579</v>
+        <v>3.039276691805723</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.07465881542147787</v>
+        <v>0.07366336454919151</v>
       </c>
       <c r="W76">
-        <v>0.2181954513236155</v>
+        <v>0.2184301786393006</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2986352616859115</v>
+        <v>0.294653458196766</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7690,22 +7690,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2142539893921362</v>
+        <v>0.2161539893921361</v>
       </c>
       <c r="C77">
-        <v>-40.06813563260606</v>
+        <v>-41.13559810673902</v>
       </c>
       <c r="D77">
-        <v>17.07686436739393</v>
+        <v>16.88640189326097</v>
       </c>
       <c r="E77">
-        <v>32.37499999999999</v>
+        <v>33.25199999999999</v>
       </c>
       <c r="F77">
-        <v>65.77499999999999</v>
+        <v>66.65199999999999</v>
       </c>
       <c r="G77">
         <v>8.630000000000001</v>
@@ -7726,37 +7726,37 @@
         <v>4.57</v>
       </c>
       <c r="M77">
-        <v>15.509745</v>
+        <v>15.7165416</v>
       </c>
       <c r="N77">
-        <v>-10.939745</v>
+        <v>-11.1465416</v>
       </c>
       <c r="O77">
-        <v>-2.73493625</v>
+        <v>-2.786635399999999</v>
       </c>
       <c r="P77">
-        <v>-8.204808749999998</v>
+        <v>-8.359906199999998</v>
       </c>
       <c r="Q77">
-        <v>-0.6248087499999979</v>
+        <v>-0.7799061999999974</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2017254216506426</v>
+        <v>0.2082223142194194</v>
       </c>
       <c r="T77">
-        <v>3.039276691805723</v>
+        <v>3.165913220630962</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.07366336454919151</v>
+        <v>0.07269410975249162</v>
       </c>
       <c r="W77">
-        <v>0.2184301786393006</v>
+        <v>0.2186587289203625</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.294653458196766</v>
+        <v>0.2907764390099665</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7772,22 +7772,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2161539893921361</v>
+        <v>0.2180539893921362</v>
       </c>
       <c r="C78">
-        <v>-41.13559810673902</v>
+        <v>-42.1988588935598</v>
       </c>
       <c r="D78">
-        <v>16.88640189326097</v>
+        <v>16.7001411064402</v>
       </c>
       <c r="E78">
-        <v>33.25199999999999</v>
+        <v>34.129</v>
       </c>
       <c r="F78">
-        <v>66.65199999999999</v>
+        <v>67.529</v>
       </c>
       <c r="G78">
         <v>8.630000000000001</v>
@@ -7808,37 +7808,37 @@
         <v>4.57</v>
       </c>
       <c r="M78">
-        <v>15.7165416</v>
+        <v>15.9233382</v>
       </c>
       <c r="N78">
-        <v>-11.1465416</v>
+        <v>-11.3533382</v>
       </c>
       <c r="O78">
-        <v>-2.786635399999999</v>
+        <v>-2.83833455</v>
       </c>
       <c r="P78">
-        <v>-8.359906199999998</v>
+        <v>-8.515003650000001</v>
       </c>
       <c r="Q78">
-        <v>-0.7799061999999974</v>
+        <v>-0.9350036500000005</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2082223142194194</v>
+        <v>0.2152841539680898</v>
       </c>
       <c r="T78">
-        <v>3.165913220630962</v>
+        <v>3.30356162152796</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.07269410975249162</v>
+        <v>0.07175003040505665</v>
       </c>
       <c r="W78">
-        <v>0.2186587289203625</v>
+        <v>0.2188813428304877</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2907764390099665</v>
+        <v>0.2870001216202266</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7854,22 +7854,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2180539893921362</v>
+        <v>0.2199539893921361</v>
       </c>
       <c r="C79">
-        <v>-42.1988588935598</v>
+        <v>-43.25805551284476</v>
       </c>
       <c r="D79">
-        <v>16.7001411064402</v>
+        <v>16.51794448715523</v>
       </c>
       <c r="E79">
-        <v>34.129</v>
+        <v>35.00599999999999</v>
       </c>
       <c r="F79">
-        <v>67.529</v>
+        <v>68.40599999999999</v>
       </c>
       <c r="G79">
         <v>8.630000000000001</v>
@@ -7890,37 +7890,37 @@
         <v>4.57</v>
       </c>
       <c r="M79">
-        <v>15.9233382</v>
+        <v>16.1301348</v>
       </c>
       <c r="N79">
-        <v>-11.3533382</v>
+        <v>-11.5601348</v>
       </c>
       <c r="O79">
-        <v>-2.83833455</v>
+        <v>-2.8900337</v>
       </c>
       <c r="P79">
-        <v>-8.515003650000001</v>
+        <v>-8.6701011</v>
       </c>
       <c r="Q79">
-        <v>-0.9350036500000005</v>
+        <v>-1.0901011</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2152841539680898</v>
+        <v>0.2229879791484576</v>
       </c>
       <c r="T79">
-        <v>3.30356162152796</v>
+        <v>3.453723513415594</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.07175003040505665</v>
+        <v>0.07083015822037644</v>
       </c>
       <c r="W79">
-        <v>0.2188813428304877</v>
+        <v>0.2190982486916352</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2870001216202266</v>
+        <v>0.2833206328815058</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7936,22 +7936,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2199539893921361</v>
+        <v>0.2218539893921362</v>
       </c>
       <c r="C80">
-        <v>-43.25805551284476</v>
+        <v>-44.31331954783739</v>
       </c>
       <c r="D80">
-        <v>16.51794448715523</v>
+        <v>16.33968045216259</v>
       </c>
       <c r="E80">
-        <v>35.00599999999999</v>
+        <v>35.88299999999999</v>
       </c>
       <c r="F80">
-        <v>68.40599999999999</v>
+        <v>69.28299999999999</v>
       </c>
       <c r="G80">
         <v>8.630000000000001</v>
@@ -7972,37 +7972,37 @@
         <v>4.57</v>
       </c>
       <c r="M80">
-        <v>16.1301348</v>
+        <v>16.3369314</v>
       </c>
       <c r="N80">
-        <v>-11.5601348</v>
+        <v>-11.7669314</v>
       </c>
       <c r="O80">
-        <v>-2.8900337</v>
+        <v>-2.941732849999999</v>
       </c>
       <c r="P80">
-        <v>-8.6701011</v>
+        <v>-8.825198549999998</v>
       </c>
       <c r="Q80">
-        <v>-1.0901011</v>
+        <v>-1.245198549999998</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2229879791484576</v>
+        <v>0.2314255019650508</v>
       </c>
       <c r="T80">
-        <v>3.453723513415594</v>
+        <v>3.618186537863957</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.07083015822037644</v>
+        <v>0.06993357393910586</v>
       </c>
       <c r="W80">
-        <v>0.2190982486916352</v>
+        <v>0.2193096632651589</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2833206328815058</v>
+        <v>0.2797342957564235</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8018,22 +8018,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2218539893921362</v>
+        <v>0.2237539893921361</v>
       </c>
       <c r="C81">
-        <v>-44.31331954783739</v>
+        <v>-45.36477696216769</v>
       </c>
       <c r="D81">
-        <v>16.33968045216259</v>
+        <v>16.16522303783231</v>
       </c>
       <c r="E81">
-        <v>35.88299999999999</v>
+        <v>36.76</v>
       </c>
       <c r="F81">
-        <v>69.28299999999999</v>
+        <v>70.16</v>
       </c>
       <c r="G81">
         <v>8.630000000000001</v>
@@ -8054,37 +8054,37 @@
         <v>4.57</v>
       </c>
       <c r="M81">
-        <v>16.3369314</v>
+        <v>16.543728</v>
       </c>
       <c r="N81">
-        <v>-11.7669314</v>
+        <v>-11.973728</v>
       </c>
       <c r="O81">
-        <v>-2.941732849999999</v>
+        <v>-2.993432</v>
       </c>
       <c r="P81">
-        <v>-8.825198549999998</v>
+        <v>-8.980296000000001</v>
       </c>
       <c r="Q81">
-        <v>-1.245198549999998</v>
+        <v>-1.400296000000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2314255019650508</v>
+        <v>0.2407067770633034</v>
       </c>
       <c r="T81">
-        <v>3.618186537863957</v>
+        <v>3.799095864757155</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.06993357393910586</v>
+        <v>0.06905940426486702</v>
       </c>
       <c r="W81">
-        <v>0.2193096632651589</v>
+        <v>0.2195157924743444</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2797342957564235</v>
+        <v>0.276237617059468</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8100,22 +8100,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2237539893921361</v>
+        <v>0.2256539893921362</v>
       </c>
       <c r="C82">
-        <v>-45.36477696216769</v>
+        <v>-46.41254839668346</v>
       </c>
       <c r="D82">
-        <v>16.16522303783231</v>
+        <v>15.99445160331653</v>
       </c>
       <c r="E82">
-        <v>36.76</v>
+        <v>37.63699999999999</v>
       </c>
       <c r="F82">
-        <v>70.16</v>
+        <v>71.03699999999999</v>
       </c>
       <c r="G82">
         <v>8.630000000000001</v>
@@ -8136,37 +8136,37 @@
         <v>4.57</v>
       </c>
       <c r="M82">
-        <v>16.543728</v>
+        <v>16.7505246</v>
       </c>
       <c r="N82">
-        <v>-11.973728</v>
+        <v>-12.1805246</v>
       </c>
       <c r="O82">
-        <v>-2.993432</v>
+        <v>-3.04513115</v>
       </c>
       <c r="P82">
-        <v>-8.980296000000001</v>
+        <v>-9.135393449999999</v>
       </c>
       <c r="Q82">
-        <v>-1.400296000000001</v>
+        <v>-1.555393449999999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2407067770633034</v>
+        <v>0.2509650284876878</v>
       </c>
       <c r="T82">
-        <v>3.799095864757155</v>
+        <v>3.999048278691742</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.06905940426486702</v>
+        <v>0.06820681902702917</v>
       </c>
       <c r="W82">
-        <v>0.2195157924743444</v>
+        <v>0.2197168320734265</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.276237617059468</v>
+        <v>0.2728272761081166</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8182,22 +8182,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2256539893921362</v>
+        <v>0.2275539893921361</v>
       </c>
       <c r="C83">
-        <v>-46.41254839668346</v>
+        <v>-47.45674944766418</v>
       </c>
       <c r="D83">
-        <v>15.99445160331653</v>
+        <v>15.82725055233582</v>
       </c>
       <c r="E83">
-        <v>37.63699999999999</v>
+        <v>38.514</v>
       </c>
       <c r="F83">
-        <v>71.03699999999999</v>
+        <v>71.914</v>
       </c>
       <c r="G83">
         <v>8.630000000000001</v>
@@ -8218,37 +8218,37 @@
         <v>4.57</v>
       </c>
       <c r="M83">
-        <v>16.7505246</v>
+        <v>16.9573212</v>
       </c>
       <c r="N83">
-        <v>-12.1805246</v>
+        <v>-12.3873212</v>
       </c>
       <c r="O83">
-        <v>-3.04513115</v>
+        <v>-3.096830300000001</v>
       </c>
       <c r="P83">
-        <v>-9.135393449999999</v>
+        <v>-9.290490900000002</v>
       </c>
       <c r="Q83">
-        <v>-1.555393449999999</v>
+        <v>-1.710490900000002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2509650284876878</v>
+        <v>0.2623630856258926</v>
       </c>
       <c r="T83">
-        <v>3.999048278691742</v>
+        <v>4.22121762750795</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.06820681902702917</v>
+        <v>0.06737502855108977</v>
       </c>
       <c r="W83">
-        <v>0.2197168320734265</v>
+        <v>0.219912968267653</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2728272761081166</v>
+        <v>0.269500114204359</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8264,22 +8264,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2275539893921361</v>
+        <v>0.2294539893921361</v>
       </c>
       <c r="C84">
-        <v>-47.45674944766418</v>
+        <v>-48.49749092776472</v>
       </c>
       <c r="D84">
-        <v>15.82725055233582</v>
+        <v>15.66350907223528</v>
       </c>
       <c r="E84">
-        <v>38.514</v>
+        <v>39.391</v>
       </c>
       <c r="F84">
-        <v>71.914</v>
+        <v>72.791</v>
       </c>
       <c r="G84">
         <v>8.630000000000001</v>
@@ -8300,37 +8300,37 @@
         <v>4.57</v>
       </c>
       <c r="M84">
-        <v>16.9573212</v>
+        <v>17.1641178</v>
       </c>
       <c r="N84">
-        <v>-12.3873212</v>
+        <v>-12.5941178</v>
       </c>
       <c r="O84">
-        <v>-3.096830300000001</v>
+        <v>-3.14852945</v>
       </c>
       <c r="P84">
-        <v>-9.290490900000002</v>
+        <v>-9.44558835</v>
       </c>
       <c r="Q84">
-        <v>-1.710490900000002</v>
+        <v>-1.865588349999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2623630856258926</v>
+        <v>0.2751020906627098</v>
       </c>
       <c r="T84">
-        <v>4.22121762750795</v>
+        <v>4.469524546773123</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.06737502855108977</v>
+        <v>0.06656328121914895</v>
       </c>
       <c r="W84">
-        <v>0.219912968267653</v>
+        <v>0.2201043782885247</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.269500114204359</v>
+        <v>0.2662531248765958</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8346,22 +8346,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2294539893921361</v>
+        <v>0.2313539893921361</v>
       </c>
       <c r="C85">
-        <v>-48.49749092776472</v>
+        <v>-49.53487911092769</v>
       </c>
       <c r="D85">
-        <v>15.66350907223528</v>
+        <v>15.5031208890723</v>
       </c>
       <c r="E85">
-        <v>39.391</v>
+        <v>40.26799999999999</v>
       </c>
       <c r="F85">
-        <v>72.791</v>
+        <v>73.66799999999999</v>
       </c>
       <c r="G85">
         <v>8.630000000000001</v>
@@ -8382,37 +8382,37 @@
         <v>4.57</v>
       </c>
       <c r="M85">
-        <v>17.1641178</v>
+        <v>17.3709144</v>
       </c>
       <c r="N85">
-        <v>-12.5941178</v>
+        <v>-12.8009144</v>
       </c>
       <c r="O85">
-        <v>-3.14852945</v>
+        <v>-3.2002286</v>
       </c>
       <c r="P85">
-        <v>-9.44558835</v>
+        <v>-9.600685800000001</v>
       </c>
       <c r="Q85">
-        <v>-1.865588349999999</v>
+        <v>-2.020685800000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2751020906627098</v>
+        <v>0.2894334713291292</v>
       </c>
       <c r="T85">
-        <v>4.469524546773123</v>
+        <v>4.748869830946444</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.06656328121914895</v>
+        <v>0.06577086120463527</v>
       </c>
       <c r="W85">
-        <v>0.2201043782885247</v>
+        <v>0.220291230927947</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2662531248765958</v>
+        <v>0.2630834448185411</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8428,22 +8428,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2313539893921361</v>
+        <v>0.2332539893921362</v>
       </c>
       <c r="C86">
-        <v>-49.53487911092769</v>
+        <v>-50.56901596240124</v>
       </c>
       <c r="D86">
-        <v>15.5031208890723</v>
+        <v>15.34598403759875</v>
       </c>
       <c r="E86">
-        <v>40.26799999999999</v>
+        <v>41.14499999999999</v>
       </c>
       <c r="F86">
-        <v>73.66799999999999</v>
+        <v>74.54499999999999</v>
       </c>
       <c r="G86">
         <v>8.630000000000001</v>
@@ -8464,37 +8464,37 @@
         <v>4.57</v>
       </c>
       <c r="M86">
-        <v>17.3709144</v>
+        <v>17.577711</v>
       </c>
       <c r="N86">
-        <v>-12.8009144</v>
+        <v>-13.007711</v>
       </c>
       <c r="O86">
-        <v>-3.2002286</v>
+        <v>-3.251927749999999</v>
       </c>
       <c r="P86">
-        <v>-9.600685800000001</v>
+        <v>-9.755783249999997</v>
       </c>
       <c r="Q86">
-        <v>-2.020685800000001</v>
+        <v>-2.175783249999997</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2894334713291291</v>
+        <v>0.305675702751071</v>
       </c>
       <c r="T86">
-        <v>4.748869830946441</v>
+        <v>5.065461153009537</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.06577086120463527</v>
+        <v>0.06499708636693369</v>
       </c>
       <c r="W86">
-        <v>0.220291230927947</v>
+        <v>0.220473687034677</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2630834448185411</v>
+        <v>0.2599883454677347</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8510,22 +8510,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2332539893921362</v>
+        <v>0.2351539893921362</v>
       </c>
       <c r="C87">
-        <v>-50.56901596240124</v>
+        <v>-51.59999935490877</v>
       </c>
       <c r="D87">
-        <v>15.34598403759875</v>
+        <v>15.19200064509121</v>
       </c>
       <c r="E87">
-        <v>41.14499999999999</v>
+        <v>42.02199999999998</v>
       </c>
       <c r="F87">
-        <v>74.54499999999999</v>
+        <v>75.42199999999998</v>
       </c>
       <c r="G87">
         <v>8.630000000000001</v>
@@ -8546,37 +8546,37 @@
         <v>4.57</v>
       </c>
       <c r="M87">
-        <v>17.577711</v>
+        <v>17.7845076</v>
       </c>
       <c r="N87">
-        <v>-13.007711</v>
+        <v>-13.2145076</v>
       </c>
       <c r="O87">
-        <v>-3.251927749999999</v>
+        <v>-3.303626899999999</v>
       </c>
       <c r="P87">
-        <v>-9.755783249999997</v>
+        <v>-9.910880699999998</v>
       </c>
       <c r="Q87">
-        <v>-2.175783249999997</v>
+        <v>-2.330880699999998</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.305675702751071</v>
+        <v>0.3242382529475761</v>
       </c>
       <c r="T87">
-        <v>5.065461153009537</v>
+        <v>5.427279806795934</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.06499708636693369</v>
+        <v>0.06424130629289956</v>
       </c>
       <c r="W87">
-        <v>0.220473687034677</v>
+        <v>0.2206518999761343</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2599883454677347</v>
+        <v>0.2569652251715983</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8592,22 +8592,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2351539893921362</v>
+        <v>0.2370539893921361</v>
       </c>
       <c r="C88">
-        <v>-51.59999935490877</v>
+        <v>-52.62792327193354</v>
       </c>
       <c r="D88">
-        <v>15.19200064509121</v>
+        <v>15.04107672806645</v>
       </c>
       <c r="E88">
-        <v>42.02199999999998</v>
+        <v>42.89899999999999</v>
       </c>
       <c r="F88">
-        <v>75.42199999999998</v>
+        <v>76.29899999999999</v>
       </c>
       <c r="G88">
         <v>8.630000000000001</v>
@@ -8628,37 +8628,37 @@
         <v>4.57</v>
       </c>
       <c r="M88">
-        <v>17.7845076</v>
+        <v>17.9913042</v>
       </c>
       <c r="N88">
-        <v>-13.2145076</v>
+        <v>-13.4213042</v>
       </c>
       <c r="O88">
-        <v>-3.303626899999999</v>
+        <v>-3.35532605</v>
       </c>
       <c r="P88">
-        <v>-9.910880699999998</v>
+        <v>-10.06597815</v>
       </c>
       <c r="Q88">
-        <v>-2.330880699999998</v>
+        <v>-2.485978149999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3242382529475761</v>
+        <v>0.3456565800973897</v>
       </c>
       <c r="T88">
-        <v>5.427279806795934</v>
+        <v>5.844762868857159</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.06424130629289956</v>
+        <v>0.06350290047344095</v>
       </c>
       <c r="W88">
-        <v>0.2206518999761343</v>
+        <v>0.2208260160683626</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2569652251715983</v>
+        <v>0.2540116018937638</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8674,22 +8674,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2370539893921361</v>
+        <v>0.2389539893921362</v>
       </c>
       <c r="C89">
-        <v>-52.62792327193354</v>
+        <v>-53.65287799900526</v>
       </c>
       <c r="D89">
-        <v>15.04107672806645</v>
+        <v>14.89312200099473</v>
       </c>
       <c r="E89">
-        <v>42.89899999999999</v>
+        <v>43.77599999999999</v>
       </c>
       <c r="F89">
-        <v>76.29899999999999</v>
+        <v>77.17599999999999</v>
       </c>
       <c r="G89">
         <v>8.630000000000001</v>
@@ -8710,37 +8710,37 @@
         <v>4.57</v>
       </c>
       <c r="M89">
-        <v>17.9913042</v>
+        <v>18.1981008</v>
       </c>
       <c r="N89">
-        <v>-13.4213042</v>
+        <v>-13.6281008</v>
       </c>
       <c r="O89">
-        <v>-3.35532605</v>
+        <v>-3.4070252</v>
       </c>
       <c r="P89">
-        <v>-10.06597815</v>
+        <v>-10.2210756</v>
       </c>
       <c r="Q89">
-        <v>-2.485978149999999</v>
+        <v>-2.641075599999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3456565800973897</v>
+        <v>0.3706446284388389</v>
       </c>
       <c r="T89">
-        <v>5.844762868857159</v>
+        <v>6.331826441261923</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.06350290047344095</v>
+        <v>0.06278127660442458</v>
       </c>
       <c r="W89">
-        <v>0.2208260160683626</v>
+        <v>0.2209961749766767</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2540116018937638</v>
+        <v>0.2511251064176983</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8756,22 +8756,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2389539893921362</v>
+        <v>0.2408539893921361</v>
       </c>
       <c r="C90">
-        <v>-53.65287799900526</v>
+        <v>-54.67495030380699</v>
       </c>
       <c r="D90">
-        <v>14.89312200099473</v>
+        <v>14.748049696193</v>
       </c>
       <c r="E90">
-        <v>43.77599999999999</v>
+        <v>44.653</v>
       </c>
       <c r="F90">
-        <v>77.17599999999999</v>
+        <v>78.053</v>
       </c>
       <c r="G90">
         <v>8.630000000000001</v>
@@ -8792,37 +8792,37 @@
         <v>4.57</v>
       </c>
       <c r="M90">
-        <v>18.1981008</v>
+        <v>18.4048974</v>
       </c>
       <c r="N90">
-        <v>-13.6281008</v>
+        <v>-13.8348974</v>
       </c>
       <c r="O90">
-        <v>-3.4070252</v>
+        <v>-3.45872435</v>
       </c>
       <c r="P90">
-        <v>-10.2210756</v>
+        <v>-10.37617305</v>
       </c>
       <c r="Q90">
-        <v>-2.641075599999999</v>
+        <v>-2.796173049999998</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3706446284388389</v>
+        <v>0.4001759582969151</v>
       </c>
       <c r="T90">
-        <v>6.331826441261923</v>
+        <v>6.907447026831188</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.06278127660442458</v>
+        <v>0.06207586900212766</v>
       </c>
       <c r="W90">
-        <v>0.2209961749766767</v>
+        <v>0.2211625100892983</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2511251064176983</v>
+        <v>0.2483034760085107</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8838,22 +8838,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2408539893921361</v>
+        <v>0.2427539893921361</v>
       </c>
       <c r="C91">
-        <v>-54.67495030380699</v>
+        <v>-55.69422360585713</v>
       </c>
       <c r="D91">
-        <v>14.748049696193</v>
+        <v>14.60577639414286</v>
       </c>
       <c r="E91">
-        <v>44.653</v>
+        <v>45.52999999999999</v>
       </c>
       <c r="F91">
-        <v>78.053</v>
+        <v>78.92999999999999</v>
       </c>
       <c r="G91">
         <v>8.630000000000001</v>
@@ -8874,37 +8874,37 @@
         <v>4.57</v>
       </c>
       <c r="M91">
-        <v>18.4048974</v>
+        <v>18.611694</v>
       </c>
       <c r="N91">
-        <v>-13.8348974</v>
+        <v>-14.041694</v>
       </c>
       <c r="O91">
-        <v>-3.45872435</v>
+        <v>-3.5104235</v>
       </c>
       <c r="P91">
-        <v>-10.37617305</v>
+        <v>-10.5312705</v>
       </c>
       <c r="Q91">
-        <v>-2.796173049999998</v>
+        <v>-2.9512705</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4001759582969151</v>
+        <v>0.4356135541266066</v>
       </c>
       <c r="T91">
-        <v>6.907447026831188</v>
+        <v>7.598191729514308</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.06207586900212766</v>
+        <v>0.06138613712432624</v>
       </c>
       <c r="W91">
-        <v>0.2211625100892983</v>
+        <v>0.2213251488660839</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2483034760085107</v>
+        <v>0.245544548497305</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8920,22 +8920,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2427539893921361</v>
+        <v>0.2446539893921362</v>
       </c>
       <c r="C92">
-        <v>-55.69422360585713</v>
+        <v>-56.71077813646374</v>
       </c>
       <c r="D92">
-        <v>14.60577639414286</v>
+        <v>14.46622186353625</v>
       </c>
       <c r="E92">
-        <v>45.52999999999999</v>
+        <v>46.40699999999999</v>
       </c>
       <c r="F92">
-        <v>78.92999999999999</v>
+        <v>79.80699999999999</v>
       </c>
       <c r="G92">
         <v>8.630000000000001</v>
@@ -8956,37 +8956,37 @@
         <v>4.57</v>
       </c>
       <c r="M92">
-        <v>18.611694</v>
+        <v>18.8184906</v>
       </c>
       <c r="N92">
-        <v>-14.041694</v>
+        <v>-14.2484906</v>
       </c>
       <c r="O92">
-        <v>-3.5104235</v>
+        <v>-3.562122649999999</v>
       </c>
       <c r="P92">
-        <v>-10.5312705</v>
+        <v>-10.68636795</v>
       </c>
       <c r="Q92">
-        <v>-2.9512705</v>
+        <v>-3.106367949999997</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4356135541266066</v>
+        <v>0.4789261712517852</v>
       </c>
       <c r="T92">
-        <v>7.598191729514308</v>
+        <v>8.442435255015898</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.06138613712432624</v>
+        <v>0.0607115641888941</v>
       </c>
       <c r="W92">
-        <v>0.2213251488660839</v>
+        <v>0.2214842131642588</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.245544548497305</v>
+        <v>0.2428462567555764</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9002,22 +9002,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2446539893921362</v>
+        <v>0.2465539893921362</v>
       </c>
       <c r="C93">
-        <v>-56.71077813646374</v>
+        <v>-57.72469108959579</v>
       </c>
       <c r="D93">
-        <v>14.46622186353625</v>
+        <v>14.3293089104042</v>
       </c>
       <c r="E93">
-        <v>46.40699999999999</v>
+        <v>47.284</v>
       </c>
       <c r="F93">
-        <v>79.80699999999999</v>
+        <v>80.684</v>
       </c>
       <c r="G93">
         <v>8.630000000000001</v>
@@ -9038,37 +9038,37 @@
         <v>4.57</v>
       </c>
       <c r="M93">
-        <v>18.8184906</v>
+        <v>19.0252872</v>
       </c>
       <c r="N93">
-        <v>-14.2484906</v>
+        <v>-14.4552872</v>
       </c>
       <c r="O93">
-        <v>-3.562122649999999</v>
+        <v>-3.6138218</v>
       </c>
       <c r="P93">
-        <v>-10.68636795</v>
+        <v>-10.8414654</v>
       </c>
       <c r="Q93">
-        <v>-3.106367949999997</v>
+        <v>-3.261465400000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4789261712517852</v>
+        <v>0.5330669426582585</v>
       </c>
       <c r="T93">
-        <v>8.442435255015898</v>
+        <v>9.497739661892888</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0607115641888941</v>
+        <v>0.06005165588249307</v>
       </c>
       <c r="W93">
-        <v>0.2214842131642588</v>
+        <v>0.2216398195429082</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2428462567555764</v>
+        <v>0.2402066235299722</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9084,22 +9084,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2465539893921362</v>
+        <v>0.2484539893921361</v>
       </c>
       <c r="C94">
-        <v>-57.72469108959579</v>
+        <v>-58.73603676426735</v>
       </c>
       <c r="D94">
-        <v>14.3293089104042</v>
+        <v>14.19496323573265</v>
       </c>
       <c r="E94">
-        <v>47.284</v>
+        <v>48.16099999999999</v>
       </c>
       <c r="F94">
-        <v>80.684</v>
+        <v>81.56099999999999</v>
       </c>
       <c r="G94">
         <v>8.630000000000001</v>
@@ -9120,37 +9120,37 @@
         <v>4.57</v>
       </c>
       <c r="M94">
-        <v>19.0252872</v>
+        <v>19.2320838</v>
       </c>
       <c r="N94">
-        <v>-14.4552872</v>
+        <v>-14.6620838</v>
       </c>
       <c r="O94">
-        <v>-3.6138218</v>
+        <v>-3.665520949999999</v>
       </c>
       <c r="P94">
-        <v>-10.8414654</v>
+        <v>-10.99656285</v>
       </c>
       <c r="Q94">
-        <v>-3.261465400000001</v>
+        <v>-3.416562849999998</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5330669426582585</v>
+        <v>0.6026765058951525</v>
       </c>
       <c r="T94">
-        <v>9.497739661892888</v>
+        <v>10.85455961359187</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06005165588249307</v>
+        <v>0.05940593915257379</v>
       </c>
       <c r="W94">
-        <v>0.2216398195429082</v>
+        <v>0.2217920795478231</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2402066235299722</v>
+        <v>0.2376237566102952</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9166,22 +9166,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2484539893921361</v>
+        <v>0.2503539893921362</v>
       </c>
       <c r="C95">
-        <v>-58.73603676426735</v>
+        <v>-59.74488669898648</v>
       </c>
       <c r="D95">
-        <v>14.19496323573265</v>
+        <v>14.06311330101351</v>
       </c>
       <c r="E95">
-        <v>48.16099999999999</v>
+        <v>49.03799999999999</v>
       </c>
       <c r="F95">
-        <v>81.56099999999999</v>
+        <v>82.43799999999999</v>
       </c>
       <c r="G95">
         <v>8.630000000000001</v>
@@ -9202,37 +9202,37 @@
         <v>4.57</v>
       </c>
       <c r="M95">
-        <v>19.2320838</v>
+        <v>19.4388804</v>
       </c>
       <c r="N95">
-        <v>-14.6620838</v>
+        <v>-14.8688804</v>
       </c>
       <c r="O95">
-        <v>-3.665520949999999</v>
+        <v>-3.7172201</v>
       </c>
       <c r="P95">
-        <v>-10.99656285</v>
+        <v>-11.1516603</v>
       </c>
       <c r="Q95">
-        <v>-3.416562849999998</v>
+        <v>-3.5716603</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6026765058951525</v>
+        <v>0.6954892568776782</v>
       </c>
       <c r="T95">
-        <v>10.85455961359187</v>
+        <v>12.66365288252386</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05940593915257379</v>
+        <v>0.05877396107648258</v>
       </c>
       <c r="W95">
-        <v>0.2217920795478231</v>
+        <v>0.2219410999781654</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2376237566102952</v>
+        <v>0.2350958443059303</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9248,22 +9248,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2503539893921362</v>
+        <v>0.2522539893921362</v>
       </c>
       <c r="C96">
-        <v>-59.74488669898648</v>
+        <v>-60.75130979878028</v>
       </c>
       <c r="D96">
-        <v>14.06311330101351</v>
+        <v>13.93369020121972</v>
       </c>
       <c r="E96">
-        <v>49.03799999999999</v>
+        <v>49.915</v>
       </c>
       <c r="F96">
-        <v>82.43799999999999</v>
+        <v>83.315</v>
       </c>
       <c r="G96">
         <v>8.630000000000001</v>
@@ -9284,37 +9284,37 @@
         <v>4.57</v>
       </c>
       <c r="M96">
-        <v>19.4388804</v>
+        <v>19.645677</v>
       </c>
       <c r="N96">
-        <v>-14.8688804</v>
+        <v>-15.075677</v>
       </c>
       <c r="O96">
-        <v>-3.7172201</v>
+        <v>-3.76891925</v>
       </c>
       <c r="P96">
-        <v>-11.1516603</v>
+        <v>-11.30675775</v>
       </c>
       <c r="Q96">
-        <v>-3.5716603</v>
+        <v>-3.726757749999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6954892568776782</v>
+        <v>0.8254271082532143</v>
       </c>
       <c r="T96">
-        <v>12.66365288252386</v>
+        <v>15.19638345902864</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05877396107648258</v>
+        <v>0.05815528780199329</v>
       </c>
       <c r="W96">
-        <v>0.2219410999781654</v>
+        <v>0.22208698313629</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2350958443059303</v>
+        <v>0.2326211512079731</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9330,22 +9330,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2522539893921362</v>
+        <v>0.2541539893921362</v>
       </c>
       <c r="C97">
-        <v>-60.75130979878028</v>
+        <v>-61.75537245526962</v>
       </c>
       <c r="D97">
-        <v>13.93369020121972</v>
+        <v>13.80662754473037</v>
       </c>
       <c r="E97">
-        <v>49.915</v>
+        <v>50.79199999999999</v>
       </c>
       <c r="F97">
-        <v>83.315</v>
+        <v>84.19199999999999</v>
       </c>
       <c r="G97">
         <v>8.630000000000001</v>
@@ -9366,37 +9366,37 @@
         <v>4.57</v>
       </c>
       <c r="M97">
-        <v>19.645677</v>
+        <v>19.8524736</v>
       </c>
       <c r="N97">
-        <v>-15.075677</v>
+        <v>-15.2824736</v>
       </c>
       <c r="O97">
-        <v>-3.76891925</v>
+        <v>-3.8206184</v>
       </c>
       <c r="P97">
-        <v>-11.30675775</v>
+        <v>-11.4618552</v>
       </c>
       <c r="Q97">
-        <v>-3.726757749999999</v>
+        <v>-3.881855199999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8254271082532143</v>
+        <v>1.020333885316518</v>
       </c>
       <c r="T97">
-        <v>15.19638345902864</v>
+        <v>18.9954793237858</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05815528780199329</v>
+        <v>0.05754950355405586</v>
       </c>
       <c r="W97">
-        <v>0.22208698313629</v>
+        <v>0.2222298270619536</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2326211512079731</v>
+        <v>0.2301980142162234</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9412,22 +9412,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2541539893921361</v>
+        <v>0.2560539893921361</v>
       </c>
       <c r="C98">
-        <v>-61.75537245526962</v>
+        <v>-62.75713866023357</v>
       </c>
       <c r="D98">
-        <v>13.80662754473038</v>
+        <v>13.68186133976642</v>
       </c>
       <c r="E98">
-        <v>50.79199999999999</v>
+        <v>51.66899999999999</v>
       </c>
       <c r="F98">
-        <v>84.19199999999999</v>
+        <v>85.06899999999999</v>
       </c>
       <c r="G98">
         <v>8.630000000000001</v>
@@ -9448,37 +9448,37 @@
         <v>4.57</v>
       </c>
       <c r="M98">
-        <v>19.8524736</v>
+        <v>20.0592702</v>
       </c>
       <c r="N98">
-        <v>-15.2824736</v>
+        <v>-15.4892702</v>
       </c>
       <c r="O98">
-        <v>-3.8206184</v>
+        <v>-3.872317549999999</v>
       </c>
       <c r="P98">
-        <v>-11.4618552</v>
+        <v>-11.61695265</v>
       </c>
       <c r="Q98">
-        <v>-3.881855199999999</v>
+        <v>-4.036952649999998</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.020333885316516</v>
+        <v>1.345178513755354</v>
       </c>
       <c r="T98">
-        <v>18.99547932378575</v>
+        <v>25.32730576504767</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05754950355405586</v>
+        <v>0.05695620970298312</v>
       </c>
       <c r="W98">
-        <v>0.2222298270619536</v>
+        <v>0.2223697257520366</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2301980142162234</v>
+        <v>0.2278248388119325</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9494,22 +9494,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2560539893921361</v>
+        <v>0.2579539893921362</v>
       </c>
       <c r="C99">
-        <v>-62.75713866023357</v>
+        <v>-63.75667011307137</v>
       </c>
       <c r="D99">
-        <v>13.68186133976642</v>
+        <v>13.55932988692861</v>
       </c>
       <c r="E99">
-        <v>51.66899999999999</v>
+        <v>52.54599999999999</v>
       </c>
       <c r="F99">
-        <v>85.06899999999999</v>
+        <v>85.94599999999998</v>
       </c>
       <c r="G99">
         <v>8.630000000000001</v>
@@ -9530,37 +9530,37 @@
         <v>4.57</v>
       </c>
       <c r="M99">
-        <v>20.0592702</v>
+        <v>20.2660668</v>
       </c>
       <c r="N99">
-        <v>-15.4892702</v>
+        <v>-15.6960668</v>
       </c>
       <c r="O99">
-        <v>-3.872317549999999</v>
+        <v>-3.924016699999999</v>
       </c>
       <c r="P99">
-        <v>-11.61695265</v>
+        <v>-11.7720501</v>
       </c>
       <c r="Q99">
-        <v>-4.036952649999998</v>
+        <v>-4.192050099999998</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.345178513755354</v>
+        <v>1.994867770633031</v>
       </c>
       <c r="T99">
-        <v>25.32730576504767</v>
+        <v>37.9909586475715</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05695620970298312</v>
+        <v>0.05637502388968738</v>
       </c>
       <c r="W99">
-        <v>0.2223697257520366</v>
+        <v>0.2225067693668117</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2278248388119325</v>
+        <v>0.2255000955587495</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9576,22 +9576,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2579539893921362</v>
+        <v>0.2598539893921362</v>
       </c>
       <c r="C100">
-        <v>-63.75667011307137</v>
+        <v>-64.75402632254136</v>
       </c>
       <c r="D100">
-        <v>13.55932988692861</v>
+        <v>13.43897367745863</v>
       </c>
       <c r="E100">
-        <v>52.54599999999999</v>
+        <v>53.42299999999999</v>
       </c>
       <c r="F100">
-        <v>85.94599999999998</v>
+        <v>86.82299999999999</v>
       </c>
       <c r="G100">
         <v>8.630000000000001</v>
@@ -9612,37 +9612,37 @@
         <v>4.57</v>
       </c>
       <c r="M100">
-        <v>20.2660668</v>
+        <v>20.4728634</v>
       </c>
       <c r="N100">
-        <v>-15.6960668</v>
+        <v>-15.9028634</v>
       </c>
       <c r="O100">
-        <v>-3.924016699999999</v>
+        <v>-3.975715849999999</v>
       </c>
       <c r="P100">
-        <v>-11.7720501</v>
+        <v>-11.92714755</v>
       </c>
       <c r="Q100">
-        <v>-4.192050099999998</v>
+        <v>-4.347147549999997</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.994867770633031</v>
+        <v>3.943935541266062</v>
       </c>
       <c r="T100">
-        <v>37.9909586475715</v>
+        <v>75.98191729514301</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05637502388968738</v>
+        <v>0.05580557920393295</v>
       </c>
       <c r="W100">
-        <v>0.2225067693668117</v>
+        <v>0.2226410444237126</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9650,91 +9650,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2255000955587495</v>
+        <v>0.2232223168157318</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2598539893921362</v>
-      </c>
-      <c r="C101">
-        <v>-64.75402632254136</v>
-      </c>
-      <c r="D101">
-        <v>13.43897367745863</v>
-      </c>
-      <c r="E101">
-        <v>53.42299999999999</v>
-      </c>
-      <c r="F101">
-        <v>86.82299999999999</v>
-      </c>
-      <c r="G101">
-        <v>8.630000000000001</v>
-      </c>
-      <c r="H101">
-        <v>54.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>12.15</v>
-      </c>
-      <c r="K101">
-        <v>7.58</v>
-      </c>
-      <c r="L101">
-        <v>4.57</v>
-      </c>
-      <c r="M101">
-        <v>20.4728634</v>
-      </c>
-      <c r="N101">
-        <v>-15.9028634</v>
-      </c>
-      <c r="O101">
-        <v>-3.975715849999999</v>
-      </c>
-      <c r="P101">
-        <v>-11.92714755</v>
-      </c>
-      <c r="Q101">
-        <v>-4.347147549999997</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.943935541266062</v>
-      </c>
-      <c r="T101">
-        <v>75.98191729514301</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05580557920393295</v>
-      </c>
-      <c r="W101">
-        <v>0.2226410444237126</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2232223168157318</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
